--- a/modulos/reportes/estadisticas/Estadistica de competencias totales.xlsx
+++ b/modulos/reportes/estadisticas/Estadistica de competencias totales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55b6a939d4276db6/INFORMES AKC/CICLO 25-26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55b6a939d4276db6/INFORMES AKC/CICLO 26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3680" documentId="11_4329AC1C95F6F2D5C6A5F808B3482A3E5370D056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E7178AC-39EE-C740-B7D0-49A30DD814B2}"/>
+  <xr:revisionPtr revIDLastSave="3787" documentId="11_4329AC1C95F6F2D5C6A5F808B3482A3E5370D056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27606152-23A9-A14B-B295-141377107C49}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Historial" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="106">
   <si>
     <t>GIMNASTA</t>
   </si>
@@ -192,9 +192,6 @@
     <t>DC 23</t>
   </si>
   <si>
-    <t>NAL DE CL 23</t>
-  </si>
-  <si>
     <t>NAC 23</t>
   </si>
   <si>
@@ -303,13 +300,7 @@
     <t>DIEGO JAIME</t>
   </si>
   <si>
-    <t>JR 22</t>
-  </si>
-  <si>
     <t>SELEC JR 24</t>
-  </si>
-  <si>
-    <t>PANAM 24</t>
   </si>
   <si>
     <t>SELEC CNAR 25</t>
@@ -330,13 +321,61 @@
     <t>FINALES DE ON 26</t>
   </si>
   <si>
-    <t>CAMPEONATO CENTROAMERICANO 27</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>FINALES CC 27</t>
+    <t>DANIEL CORRAL 25</t>
+  </si>
+  <si>
+    <t>JAIME ROMERO 25</t>
+  </si>
+  <si>
+    <t>NACIONAL 25</t>
+  </si>
+  <si>
+    <t>DANIEL CORRAL 23</t>
+  </si>
+  <si>
+    <t>NACIONAL DE CLUBS 23</t>
+  </si>
+  <si>
+    <t>NACIONAL 23</t>
+  </si>
+  <si>
+    <t>QUERETARO 22</t>
+  </si>
+  <si>
+    <t>JAIME ROMERO 24</t>
+  </si>
+  <si>
+    <t>DANIEL CORRAL 24</t>
+  </si>
+  <si>
+    <t>NACIONAL 24</t>
+  </si>
+  <si>
+    <t>NACIONAL 22</t>
+  </si>
+  <si>
+    <t>NACIONAL 21</t>
+  </si>
+  <si>
+    <t>CAMPEONATO CENTROAMERICANO 26</t>
+  </si>
+  <si>
+    <t>FINALES CC 26</t>
+  </si>
+  <si>
+    <t>JUEGOS NACIONALES CONADE 23</t>
+  </si>
+  <si>
+    <t>JAIME ROMERO 23</t>
+  </si>
+  <si>
+    <t>CAMPEONATO PANAMERICANO 24</t>
+  </si>
+  <si>
+    <t>JUEGOS NACIONALES CONADE 24</t>
   </si>
 </sst>
 </file>
@@ -547,7 +586,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -789,22 +828,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF505050"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1055,16 +1083,10 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="25" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="25" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1108,44 +1130,8 @@
     <xf numFmtId="49" fontId="0" fillId="25" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="25" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1162,14 +1148,8 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1179,33 +1159,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1233,6 +1186,85 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="13" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2409,21 +2441,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N405"/>
-  <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.44921875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="32.8203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.12890625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.78125" style="7" customWidth="1"/>
-    <col min="5" max="10" width="8.609375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="7.12890625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.3203125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="5.78125" style="7" customWidth="1"/>
-    <col min="14" max="14" width="11.43359375" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.43359375" style="1"/>
+    <col min="1" max="1" width="13.5" style="27" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.83203125" style="7" customWidth="1"/>
+    <col min="5" max="10" width="8.6640625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="7.1640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="5.83203125" style="7" customWidth="1"/>
+    <col min="14" max="14" width="11.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="69" t="s">
         <v>0</v>
       </c>
@@ -2465,7 +2497,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="106" t="s">
+      <c r="A2" s="122" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="84" t="s">
@@ -2508,7 +2540,7 @@
       <c r="N2" s="10"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="107"/>
+      <c r="A3" s="123"/>
       <c r="B3" s="85" t="s">
         <v>16</v>
       </c>
@@ -2549,7 +2581,7 @@
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="107"/>
+      <c r="A4" s="123"/>
       <c r="B4" s="85" t="s">
         <v>17</v>
       </c>
@@ -2589,10 +2621,10 @@
       </c>
       <c r="N4" s="10"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="107"/>
-      <c r="B5" s="86" t="s">
-        <v>18</v>
+    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="123"/>
+      <c r="B5" s="137" t="s">
+        <v>88</v>
       </c>
       <c r="C5" s="11">
         <v>3</v>
@@ -2630,9 +2662,9 @@
       </c>
       <c r="N5" s="10"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="107"/>
-      <c r="B6" s="87" t="s">
+    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="123"/>
+      <c r="B6" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="8">
@@ -2671,9 +2703,9 @@
       </c>
       <c r="N6" s="10"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="107"/>
-      <c r="B7" s="87" t="s">
+    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="123"/>
+      <c r="B7" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="8">
@@ -2712,9 +2744,9 @@
       </c>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="107"/>
-      <c r="B8" s="87" t="s">
+    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="123"/>
+      <c r="B8" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="8">
@@ -2753,9 +2785,9 @@
       </c>
       <c r="N8" s="10"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="107"/>
-      <c r="B9" s="87" t="s">
+    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="123"/>
+      <c r="B9" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="14">
@@ -2794,9 +2826,9 @@
       </c>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="107"/>
-      <c r="B10" s="87" t="s">
+    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="123"/>
+      <c r="B10" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="14">
@@ -2835,10 +2867,10 @@
       </c>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="108"/>
-      <c r="B11" s="88" t="s">
-        <v>85</v>
+    <row r="11" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="124"/>
+      <c r="B11" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C11" s="31">
         <v>4</v>
@@ -2877,7 +2909,7 @@
       <c r="N11" s="10"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="106" t="s">
+      <c r="A12" s="122" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="84" t="s">
@@ -2920,7 +2952,7 @@
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="107"/>
+      <c r="A13" s="123"/>
       <c r="B13" s="85" t="s">
         <v>16</v>
       </c>
@@ -2961,7 +2993,7 @@
       <c r="N13" s="10"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="107"/>
+      <c r="A14" s="123"/>
       <c r="B14" s="85" t="s">
         <v>17</v>
       </c>
@@ -3002,7 +3034,7 @@
       <c r="N14" s="10"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="107"/>
+      <c r="A15" s="123"/>
       <c r="B15" s="85" t="s">
         <v>26</v>
       </c>
@@ -3043,9 +3075,9 @@
       <c r="N15" s="10"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="107"/>
-      <c r="B16" s="89" t="s">
-        <v>27</v>
+      <c r="A16" s="123"/>
+      <c r="B16" s="138" t="s">
+        <v>89</v>
       </c>
       <c r="C16" s="11">
         <v>3</v>
@@ -3083,10 +3115,10 @@
       </c>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="107"/>
-      <c r="B17" s="86" t="s">
-        <v>18</v>
+    <row r="17" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="123"/>
+      <c r="B17" s="137" t="s">
+        <v>88</v>
       </c>
       <c r="C17" s="11">
         <v>3</v>
@@ -3124,9 +3156,9 @@
       </c>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="107"/>
-      <c r="B18" s="87" t="s">
+    <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="123"/>
+      <c r="B18" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="8">
@@ -3165,9 +3197,9 @@
       </c>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="107"/>
-      <c r="B19" s="87" t="s">
+    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="123"/>
+      <c r="B19" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="8">
@@ -3206,9 +3238,9 @@
       </c>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="107"/>
-      <c r="B20" s="87" t="s">
+    <row r="20" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="123"/>
+      <c r="B20" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="8">
@@ -3247,9 +3279,9 @@
       </c>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="107"/>
-      <c r="B21" s="87" t="s">
+    <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="123"/>
+      <c r="B21" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="8">
@@ -3288,10 +3320,10 @@
       </c>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="108"/>
-      <c r="B22" s="88" t="s">
-        <v>85</v>
+    <row r="22" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="124"/>
+      <c r="B22" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C22" s="31">
         <v>4</v>
@@ -3330,7 +3362,7 @@
       <c r="N22" s="10"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="106" t="s">
+      <c r="A23" s="122" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="84" t="s">
@@ -3373,7 +3405,7 @@
       <c r="N23" s="10"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="107"/>
+      <c r="A24" s="123"/>
       <c r="B24" s="85" t="s">
         <v>17</v>
       </c>
@@ -3414,7 +3446,7 @@
       <c r="N24" s="10"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="107"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="85" t="s">
         <v>26</v>
       </c>
@@ -3455,9 +3487,9 @@
       <c r="N25" s="10"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="107"/>
-      <c r="B26" s="89" t="s">
-        <v>27</v>
+      <c r="A26" s="123"/>
+      <c r="B26" s="138" t="s">
+        <v>89</v>
       </c>
       <c r="C26" s="11">
         <v>3</v>
@@ -3495,10 +3527,10 @@
       </c>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="107"/>
-      <c r="B27" s="86" t="s">
-        <v>18</v>
+    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="123"/>
+      <c r="B27" s="137" t="s">
+        <v>88</v>
       </c>
       <c r="C27" s="11">
         <v>3</v>
@@ -3536,9 +3568,9 @@
       </c>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="107"/>
-      <c r="B28" s="87" t="s">
+    <row r="28" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="123"/>
+      <c r="B28" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="8">
@@ -3577,9 +3609,9 @@
       </c>
       <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="107"/>
-      <c r="B29" s="87" t="s">
+    <row r="29" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="123"/>
+      <c r="B29" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="8">
@@ -3618,9 +3650,9 @@
       </c>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="107"/>
-      <c r="B30" s="87" t="s">
+    <row r="30" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="123"/>
+      <c r="B30" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="8">
@@ -3660,9 +3692,9 @@
       <c r="N30" s="10"/>
     </row>
     <row r="31" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="108"/>
-      <c r="B31" s="88" t="s">
-        <v>85</v>
+      <c r="A31" s="124"/>
+      <c r="B31" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C31" s="31">
         <v>4</v>
@@ -3701,7 +3733,7 @@
       <c r="N31" s="10"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="106" t="s">
+      <c r="A32" s="122" t="s">
         <v>29</v>
       </c>
       <c r="B32" s="84" t="s">
@@ -3744,7 +3776,7 @@
       <c r="N32" s="10"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="107"/>
+      <c r="A33" s="123"/>
       <c r="B33" s="85" t="s">
         <v>16</v>
       </c>
@@ -3785,7 +3817,7 @@
       <c r="N33" s="10"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="107"/>
+      <c r="A34" s="123"/>
       <c r="B34" s="85" t="s">
         <v>17</v>
       </c>
@@ -3826,7 +3858,7 @@
       <c r="N34" s="10"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="107"/>
+      <c r="A35" s="123"/>
       <c r="B35" s="85" t="s">
         <v>26</v>
       </c>
@@ -3867,9 +3899,9 @@
       <c r="N35" s="10"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="107"/>
-      <c r="B36" s="89" t="s">
-        <v>27</v>
+      <c r="A36" s="123"/>
+      <c r="B36" s="138" t="s">
+        <v>89</v>
       </c>
       <c r="C36" s="11">
         <v>3</v>
@@ -3907,10 +3939,10 @@
       </c>
       <c r="N36" s="10"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="107"/>
-      <c r="B37" s="86" t="s">
-        <v>18</v>
+    <row r="37" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="123"/>
+      <c r="B37" s="137" t="s">
+        <v>88</v>
       </c>
       <c r="C37" s="11">
         <v>3</v>
@@ -3948,9 +3980,9 @@
       </c>
       <c r="N37" s="10"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="107"/>
-      <c r="B38" s="87" t="s">
+    <row r="38" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="123"/>
+      <c r="B38" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C38" s="8">
@@ -3989,9 +4021,9 @@
       </c>
       <c r="N38" s="10"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="107"/>
-      <c r="B39" s="87" t="s">
+    <row r="39" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="123"/>
+      <c r="B39" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C39" s="8">
@@ -4030,9 +4062,9 @@
       </c>
       <c r="N39" s="10"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="107"/>
-      <c r="B40" s="87" t="s">
+    <row r="40" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="123"/>
+      <c r="B40" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C40" s="8">
@@ -4071,9 +4103,9 @@
       </c>
       <c r="N40" s="10"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="107"/>
-      <c r="B41" s="87" t="s">
+    <row r="41" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="123"/>
+      <c r="B41" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C41" s="8">
@@ -4112,9 +4144,9 @@
       </c>
       <c r="N41" s="10"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="107"/>
-      <c r="B42" s="87" t="s">
+    <row r="42" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="123"/>
+      <c r="B42" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="8">
@@ -4154,9 +4186,9 @@
       <c r="N42" s="10"/>
     </row>
     <row r="43" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="108"/>
-      <c r="B43" s="88" t="s">
-        <v>85</v>
+      <c r="A43" s="124"/>
+      <c r="B43" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C43" s="31">
         <v>4</v>
@@ -4195,10 +4227,10 @@
       <c r="N43" s="10"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="106" t="s">
+      <c r="A44" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="90" t="s">
+      <c r="B44" s="88" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="28">
@@ -4238,7 +4270,7 @@
       <c r="N44" s="10"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" s="107"/>
+      <c r="A45" s="123"/>
       <c r="B45" s="85" t="s">
         <v>17</v>
       </c>
@@ -4279,7 +4311,7 @@
       <c r="N45" s="10"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="107"/>
+      <c r="A46" s="123"/>
       <c r="B46" s="85" t="s">
         <v>26</v>
       </c>
@@ -4320,9 +4352,9 @@
       <c r="N46" s="10"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" s="107"/>
-      <c r="B47" s="89" t="s">
-        <v>27</v>
+      <c r="A47" s="123"/>
+      <c r="B47" s="138" t="s">
+        <v>89</v>
       </c>
       <c r="C47" s="11">
         <v>3</v>
@@ -4360,10 +4392,10 @@
       </c>
       <c r="N47" s="10"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48" s="107"/>
-      <c r="B48" s="86" t="s">
-        <v>18</v>
+    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="123"/>
+      <c r="B48" s="137" t="s">
+        <v>88</v>
       </c>
       <c r="C48" s="11">
         <v>3</v>
@@ -4401,9 +4433,9 @@
       </c>
       <c r="N48" s="10"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" s="107"/>
-      <c r="B49" s="87" t="s">
+    <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="123"/>
+      <c r="B49" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C49" s="8">
@@ -4442,9 +4474,9 @@
       </c>
       <c r="N49" s="10"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="107"/>
-      <c r="B50" s="87" t="s">
+    <row r="50" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="123"/>
+      <c r="B50" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="8">
@@ -4483,9 +4515,9 @@
       </c>
       <c r="N50" s="10"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" s="107"/>
-      <c r="B51" s="87" t="s">
+    <row r="51" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="123"/>
+      <c r="B51" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="8">
@@ -4524,9 +4556,9 @@
       </c>
       <c r="N51" s="10"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="107"/>
-      <c r="B52" s="87" t="s">
+    <row r="52" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="123"/>
+      <c r="B52" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="8">
@@ -4566,9 +4598,9 @@
       <c r="N52" s="10"/>
     </row>
     <row r="53" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="108"/>
-      <c r="B53" s="88" t="s">
-        <v>85</v>
+      <c r="A53" s="124"/>
+      <c r="B53" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C53" s="31">
         <v>4</v>
@@ -4607,10 +4639,10 @@
       <c r="N53" s="10"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="106" t="s">
+      <c r="A54" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="B54" s="90" t="s">
+      <c r="B54" s="88" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="28">
@@ -4650,7 +4682,7 @@
       <c r="N54" s="10"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="107"/>
+      <c r="A55" s="123"/>
       <c r="B55" s="85" t="s">
         <v>17</v>
       </c>
@@ -4691,7 +4723,7 @@
       <c r="N55" s="10"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" s="107"/>
+      <c r="A56" s="123"/>
       <c r="B56" s="85" t="s">
         <v>26</v>
       </c>
@@ -4732,9 +4764,9 @@
       <c r="N56" s="10"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" s="107"/>
-      <c r="B57" s="85" t="s">
-        <v>27</v>
+      <c r="A57" s="123"/>
+      <c r="B57" s="139" t="s">
+        <v>89</v>
       </c>
       <c r="C57" s="11">
         <v>3</v>
@@ -4772,9 +4804,9 @@
       </c>
       <c r="N57" s="10"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="107"/>
-      <c r="B58" s="87" t="s">
+    <row r="58" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="123"/>
+      <c r="B58" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C58" s="8">
@@ -4813,9 +4845,9 @@
       </c>
       <c r="N58" s="10"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" s="107"/>
-      <c r="B59" s="87" t="s">
+    <row r="59" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="123"/>
+      <c r="B59" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C59" s="8">
@@ -4854,9 +4886,9 @@
       </c>
       <c r="N59" s="10"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" s="107"/>
-      <c r="B60" s="87" t="s">
+    <row r="60" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="123"/>
+      <c r="B60" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C60" s="8">
@@ -4895,9 +4927,9 @@
       </c>
       <c r="N60" s="10"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61" s="107"/>
-      <c r="B61" s="87" t="s">
+    <row r="61" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="123"/>
+      <c r="B61" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="8">
@@ -4937,9 +4969,9 @@
       <c r="N61" s="10"/>
     </row>
     <row r="62" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="108"/>
-      <c r="B62" s="88" t="s">
-        <v>85</v>
+      <c r="A62" s="124"/>
+      <c r="B62" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C62" s="31">
         <v>4</v>
@@ -4978,7 +5010,7 @@
       <c r="N62" s="10"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" s="106" t="s">
+      <c r="A63" s="122" t="s">
         <v>32</v>
       </c>
       <c r="B63" s="84" t="s">
@@ -5021,7 +5053,7 @@
       <c r="N63" s="10"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64" s="107"/>
+      <c r="A64" s="123"/>
       <c r="B64" s="85" t="s">
         <v>16</v>
       </c>
@@ -5062,7 +5094,7 @@
       <c r="N64" s="10"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="107"/>
+      <c r="A65" s="123"/>
       <c r="B65" s="85" t="s">
         <v>17</v>
       </c>
@@ -5103,7 +5135,7 @@
       <c r="N65" s="10"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="107"/>
+      <c r="A66" s="123"/>
       <c r="B66" s="85" t="s">
         <v>26</v>
       </c>
@@ -5144,9 +5176,9 @@
       <c r="N66" s="10"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="107"/>
-      <c r="B67" s="89" t="s">
-        <v>27</v>
+      <c r="A67" s="123"/>
+      <c r="B67" s="138" t="s">
+        <v>89</v>
       </c>
       <c r="C67" s="11">
         <v>3</v>
@@ -5184,10 +5216,10 @@
       </c>
       <c r="N67" s="10"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" s="107"/>
-      <c r="B68" s="86" t="s">
-        <v>18</v>
+    <row r="68" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="123"/>
+      <c r="B68" s="137" t="s">
+        <v>88</v>
       </c>
       <c r="C68" s="11">
         <v>3</v>
@@ -5225,9 +5257,9 @@
       </c>
       <c r="N68" s="10"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" s="107"/>
-      <c r="B69" s="87" t="s">
+    <row r="69" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A69" s="123"/>
+      <c r="B69" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C69" s="11">
@@ -5266,9 +5298,9 @@
       </c>
       <c r="N69" s="10"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" s="107"/>
-      <c r="B70" s="87" t="s">
+    <row r="70" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A70" s="123"/>
+      <c r="B70" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C70" s="8">
@@ -5307,9 +5339,9 @@
       </c>
       <c r="N70" s="10"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A71" s="107"/>
-      <c r="B71" s="87" t="s">
+    <row r="71" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A71" s="123"/>
+      <c r="B71" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C71" s="8">
@@ -5348,9 +5380,9 @@
       </c>
       <c r="N71" s="10"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A72" s="107"/>
-      <c r="B72" s="87" t="s">
+    <row r="72" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A72" s="123"/>
+      <c r="B72" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="8">
@@ -5390,9 +5422,9 @@
       <c r="N72" s="10"/>
     </row>
     <row r="73" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="108"/>
-      <c r="B73" s="88" t="s">
-        <v>85</v>
+      <c r="A73" s="124"/>
+      <c r="B73" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C73" s="31">
         <v>4</v>
@@ -5431,10 +5463,10 @@
       <c r="N73" s="10"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A74" s="106" t="s">
+      <c r="A74" s="122" t="s">
         <v>33</v>
       </c>
-      <c r="B74" s="90" t="s">
+      <c r="B74" s="88" t="s">
         <v>17</v>
       </c>
       <c r="C74" s="28">
@@ -5474,7 +5506,7 @@
       <c r="N74" s="10"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A75" s="107"/>
+      <c r="A75" s="123"/>
       <c r="B75" s="85" t="s">
         <v>26</v>
       </c>
@@ -5515,9 +5547,9 @@
       <c r="N75" s="10"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A76" s="107"/>
-      <c r="B76" s="85" t="s">
-        <v>18</v>
+      <c r="A76" s="123"/>
+      <c r="B76" s="139" t="s">
+        <v>88</v>
       </c>
       <c r="C76" s="11">
         <v>3</v>
@@ -5555,9 +5587,9 @@
       </c>
       <c r="N76" s="10"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A77" s="107"/>
-      <c r="B77" s="87" t="s">
+    <row r="77" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A77" s="123"/>
+      <c r="B77" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C77" s="11">
@@ -5596,9 +5628,9 @@
       </c>
       <c r="N77" s="10"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A78" s="107"/>
-      <c r="B78" s="87" t="s">
+    <row r="78" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A78" s="123"/>
+      <c r="B78" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C78" s="11">
@@ -5637,9 +5669,9 @@
       </c>
       <c r="N78" s="10"/>
     </row>
-    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="108"/>
-      <c r="B79" s="91" t="s">
+    <row r="79" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="124"/>
+      <c r="B79" s="89" t="s">
         <v>23</v>
       </c>
       <c r="C79" s="64">
@@ -5679,7 +5711,7 @@
       <c r="N79" s="10"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A80" s="106" t="s">
+      <c r="A80" s="122" t="s">
         <v>36</v>
       </c>
       <c r="B80" s="84" t="s">
@@ -5722,7 +5754,7 @@
       <c r="N80" s="10"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A81" s="107"/>
+      <c r="A81" s="123"/>
       <c r="B81" s="85" t="s">
         <v>16</v>
       </c>
@@ -5763,7 +5795,7 @@
       <c r="N81" s="10"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A82" s="107"/>
+      <c r="A82" s="123"/>
       <c r="B82" s="85" t="s">
         <v>17</v>
       </c>
@@ -5804,7 +5836,7 @@
       <c r="N82" s="10"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A83" s="107"/>
+      <c r="A83" s="123"/>
       <c r="B83" s="85" t="s">
         <v>26</v>
       </c>
@@ -5845,9 +5877,9 @@
       <c r="N83" s="10"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A84" s="107"/>
-      <c r="B84" s="89" t="s">
-        <v>27</v>
+      <c r="A84" s="123"/>
+      <c r="B84" s="138" t="s">
+        <v>89</v>
       </c>
       <c r="C84" s="11">
         <v>3</v>
@@ -5885,10 +5917,10 @@
       </c>
       <c r="N84" s="10"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A85" s="107"/>
-      <c r="B85" s="86" t="s">
-        <v>18</v>
+    <row r="85" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A85" s="123"/>
+      <c r="B85" s="137" t="s">
+        <v>88</v>
       </c>
       <c r="C85" s="11">
         <v>3</v>
@@ -5926,9 +5958,9 @@
       </c>
       <c r="N85" s="10"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A86" s="107"/>
-      <c r="B86" s="87" t="s">
+    <row r="86" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A86" s="123"/>
+      <c r="B86" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C86" s="11">
@@ -5967,9 +5999,9 @@
       </c>
       <c r="N86" s="10"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A87" s="107"/>
-      <c r="B87" s="87" t="s">
+    <row r="87" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A87" s="123"/>
+      <c r="B87" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C87" s="11">
@@ -6008,9 +6040,9 @@
       </c>
       <c r="N87" s="10"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A88" s="107"/>
-      <c r="B88" s="87" t="s">
+    <row r="88" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A88" s="123"/>
+      <c r="B88" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C88" s="11">
@@ -6049,9 +6081,9 @@
       </c>
       <c r="N88" s="10"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A89" s="107"/>
-      <c r="B89" s="87" t="s">
+    <row r="89" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A89" s="123"/>
+      <c r="B89" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C89" s="11">
@@ -6091,9 +6123,9 @@
       <c r="N89" s="10"/>
     </row>
     <row r="90" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="108"/>
-      <c r="B90" s="88" t="s">
-        <v>85</v>
+      <c r="A90" s="124"/>
+      <c r="B90" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C90" s="31">
         <v>4</v>
@@ -6132,10 +6164,10 @@
       <c r="N90" s="10"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A91" s="106" t="s">
+      <c r="A91" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="B91" s="90" t="s">
+      <c r="B91" s="88" t="s">
         <v>16</v>
       </c>
       <c r="C91" s="28">
@@ -6175,7 +6207,7 @@
       <c r="N91" s="10"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A92" s="107"/>
+      <c r="A92" s="123"/>
       <c r="B92" s="85" t="s">
         <v>17</v>
       </c>
@@ -6216,7 +6248,7 @@
       <c r="N92" s="10"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A93" s="107"/>
+      <c r="A93" s="123"/>
       <c r="B93" s="85" t="s">
         <v>26</v>
       </c>
@@ -6257,9 +6289,9 @@
       <c r="N93" s="10"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A94" s="107"/>
-      <c r="B94" s="89" t="s">
-        <v>27</v>
+      <c r="A94" s="123"/>
+      <c r="B94" s="138" t="s">
+        <v>89</v>
       </c>
       <c r="C94" s="11">
         <v>3</v>
@@ -6297,10 +6329,10 @@
       </c>
       <c r="N94" s="10"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A95" s="107"/>
-      <c r="B95" s="86" t="s">
-        <v>18</v>
+    <row r="95" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A95" s="123"/>
+      <c r="B95" s="137" t="s">
+        <v>88</v>
       </c>
       <c r="C95" s="11">
         <v>3</v>
@@ -6338,9 +6370,9 @@
       </c>
       <c r="N95" s="10"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A96" s="107"/>
-      <c r="B96" s="87" t="s">
+    <row r="96" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A96" s="123"/>
+      <c r="B96" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C96" s="11">
@@ -6379,9 +6411,9 @@
       </c>
       <c r="N96" s="10"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A97" s="107"/>
-      <c r="B97" s="87" t="s">
+    <row r="97" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A97" s="123"/>
+      <c r="B97" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C97" s="11">
@@ -6420,9 +6452,9 @@
       </c>
       <c r="N97" s="10"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A98" s="107"/>
-      <c r="B98" s="87" t="s">
+    <row r="98" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A98" s="123"/>
+      <c r="B98" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C98" s="14">
@@ -6461,9 +6493,9 @@
       </c>
       <c r="N98" s="10"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A99" s="107"/>
-      <c r="B99" s="87" t="s">
+    <row r="99" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A99" s="123"/>
+      <c r="B99" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C99" s="14">
@@ -6503,9 +6535,9 @@
       <c r="N99" s="10"/>
     </row>
     <row r="100" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="108"/>
-      <c r="B100" s="88" t="s">
-        <v>85</v>
+      <c r="A100" s="124"/>
+      <c r="B100" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C100" s="31">
         <v>4</v>
@@ -6544,11 +6576,11 @@
       <c r="N100" s="10"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A101" s="113" t="s">
+      <c r="A101" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="B101" s="92" t="s">
-        <v>39</v>
+      <c r="B101" s="90" t="s">
+        <v>90</v>
       </c>
       <c r="C101" s="62">
         <v>4</v>
@@ -6586,9 +6618,9 @@
       </c>
       <c r="N101" s="10"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A102" s="114"/>
-      <c r="B102" s="87" t="s">
+    <row r="102" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A102" s="129"/>
+      <c r="B102" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C102" s="11">
@@ -6627,9 +6659,9 @@
       </c>
       <c r="N102" s="10"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A103" s="114"/>
-      <c r="B103" s="87" t="s">
+    <row r="103" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A103" s="129"/>
+      <c r="B103" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C103" s="11">
@@ -6668,9 +6700,9 @@
       </c>
       <c r="N103" s="10"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A104" s="114"/>
-      <c r="B104" s="87" t="s">
+    <row r="104" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A104" s="129"/>
+      <c r="B104" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C104" s="11">
@@ -6709,9 +6741,9 @@
       </c>
       <c r="N104" s="10"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A105" s="114"/>
-      <c r="B105" s="87" t="s">
+    <row r="105" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A105" s="129"/>
+      <c r="B105" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C105" s="14">
@@ -6750,9 +6782,9 @@
       </c>
       <c r="N105" s="10"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A106" s="114"/>
-      <c r="B106" s="87" t="s">
+    <row r="106" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A106" s="129"/>
+      <c r="B106" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C106" s="14">
@@ -6792,9 +6824,9 @@
       <c r="N106" s="10"/>
     </row>
     <row r="107" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="115"/>
-      <c r="B107" s="88" t="s">
-        <v>85</v>
+      <c r="A107" s="130"/>
+      <c r="B107" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C107" s="31">
         <v>4</v>
@@ -6833,10 +6865,10 @@
       <c r="N107" s="10"/>
     </row>
     <row r="108" spans="1:14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="110" t="s">
+      <c r="A108" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="B108" s="93" t="s">
+      <c r="B108" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C108" s="59" t="s">
@@ -6876,9 +6908,9 @@
       <c r="N108" s="16"/>
     </row>
     <row r="109" spans="1:14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="111"/>
-      <c r="B109" s="94" t="s">
-        <v>43</v>
+      <c r="A109" s="126"/>
+      <c r="B109" s="140" t="s">
+        <v>91</v>
       </c>
       <c r="C109" s="17">
         <v>3</v>
@@ -6917,9 +6949,9 @@
       <c r="N109" s="16"/>
     </row>
     <row r="110" spans="1:14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="111"/>
-      <c r="B110" s="94" t="s">
-        <v>44</v>
+      <c r="A110" s="126"/>
+      <c r="B110" s="140" t="s">
+        <v>92</v>
       </c>
       <c r="C110" s="17">
         <v>3</v>
@@ -6958,9 +6990,9 @@
       <c r="N110" s="16"/>
     </row>
     <row r="111" spans="1:14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="111"/>
-      <c r="B111" s="94" t="s">
-        <v>45</v>
+      <c r="A111" s="126"/>
+      <c r="B111" s="140" t="s">
+        <v>93</v>
       </c>
       <c r="C111" s="17">
         <v>4</v>
@@ -6999,8 +7031,8 @@
       <c r="N111" s="16"/>
     </row>
     <row r="112" spans="1:14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="111"/>
-      <c r="B112" s="94" t="s">
+      <c r="A112" s="126"/>
+      <c r="B112" s="92" t="s">
         <v>16</v>
       </c>
       <c r="C112" s="17">
@@ -7040,7 +7072,7 @@
       <c r="N112" s="16"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A113" s="111"/>
+      <c r="A113" s="126"/>
       <c r="B113" s="85" t="s">
         <v>17</v>
       </c>
@@ -7081,7 +7113,7 @@
       <c r="N113" s="10"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A114" s="111"/>
+      <c r="A114" s="126"/>
       <c r="B114" s="85" t="s">
         <v>26</v>
       </c>
@@ -7122,9 +7154,9 @@
       <c r="N114" s="10"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A115" s="111"/>
-      <c r="B115" s="85" t="s">
-        <v>27</v>
+      <c r="A115" s="126"/>
+      <c r="B115" s="139" t="s">
+        <v>89</v>
       </c>
       <c r="C115" s="11">
         <v>3</v>
@@ -7162,9 +7194,9 @@
       </c>
       <c r="N115" s="10"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A116" s="111"/>
-      <c r="B116" s="87" t="s">
+    <row r="116" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A116" s="126"/>
+      <c r="B116" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C116" s="11">
@@ -7203,9 +7235,9 @@
       </c>
       <c r="N116" s="10"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A117" s="111"/>
-      <c r="B117" s="87" t="s">
+    <row r="117" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A117" s="126"/>
+      <c r="B117" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C117" s="11">
@@ -7244,9 +7276,9 @@
       </c>
       <c r="N117" s="10"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A118" s="111"/>
-      <c r="B118" s="87" t="s">
+    <row r="118" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A118" s="126"/>
+      <c r="B118" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C118" s="14">
@@ -7285,9 +7317,9 @@
       </c>
       <c r="N118" s="10"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A119" s="111"/>
-      <c r="B119" s="87" t="s">
+    <row r="119" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A119" s="126"/>
+      <c r="B119" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="14">
@@ -7327,9 +7359,9 @@
       <c r="N119" s="10"/>
     </row>
     <row r="120" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="112"/>
-      <c r="B120" s="88" t="s">
-        <v>85</v>
+      <c r="A120" s="127"/>
+      <c r="B120" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C120" s="31">
         <v>4</v>
@@ -7368,8 +7400,8 @@
       <c r="N120" s="10"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A121" s="106" t="s">
-        <v>46</v>
+      <c r="A121" s="122" t="s">
+        <v>45</v>
       </c>
       <c r="B121" s="84" t="s">
         <v>14</v>
@@ -7411,7 +7443,7 @@
       <c r="N121" s="10"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A122" s="107"/>
+      <c r="A122" s="123"/>
       <c r="B122" s="85" t="s">
         <v>16</v>
       </c>
@@ -7452,7 +7484,7 @@
       <c r="N122" s="10"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A123" s="107"/>
+      <c r="A123" s="123"/>
       <c r="B123" s="85" t="s">
         <v>17</v>
       </c>
@@ -7493,7 +7525,7 @@
       <c r="N123" s="10"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A124" s="107"/>
+      <c r="A124" s="123"/>
       <c r="B124" s="85" t="s">
         <v>26</v>
       </c>
@@ -7534,9 +7566,9 @@
       <c r="N124" s="10"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A125" s="107"/>
-      <c r="B125" s="85" t="s">
-        <v>27</v>
+      <c r="A125" s="123"/>
+      <c r="B125" s="139" t="s">
+        <v>89</v>
       </c>
       <c r="C125" s="11">
         <v>4</v>
@@ -7575,9 +7607,9 @@
       <c r="N125" s="10"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A126" s="107"/>
-      <c r="B126" s="85" t="s">
-        <v>18</v>
+      <c r="A126" s="123"/>
+      <c r="B126" s="139" t="s">
+        <v>88</v>
       </c>
       <c r="C126" s="11">
         <v>4</v>
@@ -7616,9 +7648,9 @@
       <c r="N126" s="10"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A127" s="107"/>
-      <c r="B127" s="95" t="s">
-        <v>39</v>
+      <c r="A127" s="123"/>
+      <c r="B127" s="93" t="s">
+        <v>90</v>
       </c>
       <c r="C127" s="8">
         <v>4</v>
@@ -7656,9 +7688,9 @@
       </c>
       <c r="N127" s="10"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A128" s="107"/>
-      <c r="B128" s="87" t="s">
+    <row r="128" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A128" s="123"/>
+      <c r="B128" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C128" s="8">
@@ -7697,9 +7729,9 @@
       </c>
       <c r="N128" s="10"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A129" s="107"/>
-      <c r="B129" s="87" t="s">
+    <row r="129" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A129" s="123"/>
+      <c r="B129" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C129" s="8">
@@ -7738,9 +7770,9 @@
       </c>
       <c r="N129" s="10"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A130" s="107"/>
-      <c r="B130" s="87" t="s">
+    <row r="130" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A130" s="123"/>
+      <c r="B130" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C130" s="8">
@@ -7779,9 +7811,9 @@
       </c>
       <c r="N130" s="10"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A131" s="107"/>
-      <c r="B131" s="87" t="s">
+    <row r="131" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A131" s="123"/>
+      <c r="B131" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C131" s="8">
@@ -7821,9 +7853,9 @@
       <c r="N131" s="10"/>
     </row>
     <row r="132" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="108"/>
-      <c r="B132" s="88" t="s">
-        <v>85</v>
+      <c r="A132" s="124"/>
+      <c r="B132" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C132" s="31">
         <v>5</v>
@@ -7862,14 +7894,14 @@
       <c r="N132" s="10"/>
     </row>
     <row r="133" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="106" t="s">
-        <v>47</v>
-      </c>
-      <c r="B133" s="96" t="s">
+      <c r="A133" s="122" t="s">
+        <v>46</v>
+      </c>
+      <c r="B133" s="141" t="s">
+        <v>94</v>
+      </c>
+      <c r="C133" s="34" t="s">
         <v>48</v>
-      </c>
-      <c r="C133" s="34" t="s">
-        <v>49</v>
       </c>
       <c r="D133" s="29" t="s">
         <v>15</v>
@@ -7905,12 +7937,12 @@
       <c r="N133" s="10"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A134" s="107"/>
-      <c r="B134" s="97" t="s">
+      <c r="A134" s="123"/>
+      <c r="B134" s="95" t="s">
+        <v>49</v>
+      </c>
+      <c r="C134" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="C134" s="12" t="s">
-        <v>51</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>15</v>
@@ -7946,9 +7978,9 @@
       <c r="N134" s="10"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A135" s="107"/>
-      <c r="B135" s="97" t="s">
-        <v>43</v>
+      <c r="A135" s="123"/>
+      <c r="B135" s="142" t="s">
+        <v>91</v>
       </c>
       <c r="C135" s="11">
         <v>3</v>
@@ -7987,9 +8019,9 @@
       <c r="N135" s="10"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A136" s="107"/>
-      <c r="B136" s="97" t="s">
-        <v>44</v>
+      <c r="A136" s="123"/>
+      <c r="B136" s="142" t="s">
+        <v>92</v>
       </c>
       <c r="C136" s="11">
         <v>3</v>
@@ -8028,9 +8060,9 @@
       <c r="N136" s="10"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A137" s="107"/>
-      <c r="B137" s="98" t="s">
-        <v>52</v>
+      <c r="A137" s="123"/>
+      <c r="B137" s="96" t="s">
+        <v>51</v>
       </c>
       <c r="C137" s="11">
         <v>4</v>
@@ -8069,9 +8101,9 @@
       <c r="N137" s="10"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A138" s="107"/>
-      <c r="B138" s="98" t="s">
-        <v>53</v>
+      <c r="A138" s="123"/>
+      <c r="B138" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C138" s="11">
         <v>4</v>
@@ -8110,9 +8142,9 @@
       <c r="N138" s="10"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A139" s="107"/>
-      <c r="B139" s="98" t="s">
-        <v>54</v>
+      <c r="A139" s="123"/>
+      <c r="B139" s="143" t="s">
+        <v>95</v>
       </c>
       <c r="C139" s="11">
         <v>4</v>
@@ -8151,9 +8183,9 @@
       <c r="N139" s="10"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A140" s="107"/>
-      <c r="B140" s="98" t="s">
-        <v>55</v>
+      <c r="A140" s="123"/>
+      <c r="B140" s="143" t="s">
+        <v>96</v>
       </c>
       <c r="C140" s="11">
         <v>4</v>
@@ -8192,9 +8224,9 @@
       <c r="N140" s="10"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A141" s="107"/>
-      <c r="B141" s="98" t="s">
-        <v>56</v>
+      <c r="A141" s="123"/>
+      <c r="B141" s="143" t="s">
+        <v>97</v>
       </c>
       <c r="C141" s="11">
         <v>4</v>
@@ -8233,7 +8265,7 @@
       <c r="N141" s="10"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A142" s="107"/>
+      <c r="A142" s="123"/>
       <c r="B142" s="85" t="s">
         <v>16</v>
       </c>
@@ -8274,7 +8306,7 @@
       <c r="N142" s="10"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A143" s="107"/>
+      <c r="A143" s="123"/>
       <c r="B143" s="85" t="s">
         <v>17</v>
       </c>
@@ -8315,7 +8347,7 @@
       <c r="N143" s="10"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A144" s="107"/>
+      <c r="A144" s="123"/>
       <c r="B144" s="85" t="s">
         <v>26</v>
       </c>
@@ -8356,9 +8388,9 @@
       <c r="N144" s="10"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A145" s="107"/>
-      <c r="B145" s="85" t="s">
-        <v>27</v>
+      <c r="A145" s="123"/>
+      <c r="B145" s="139" t="s">
+        <v>89</v>
       </c>
       <c r="C145" s="11">
         <v>4</v>
@@ -8397,9 +8429,9 @@
       <c r="N145" s="10"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A146" s="107"/>
-      <c r="B146" s="85" t="s">
-        <v>18</v>
+      <c r="A146" s="123"/>
+      <c r="B146" s="139" t="s">
+        <v>88</v>
       </c>
       <c r="C146" s="11">
         <v>4</v>
@@ -8438,9 +8470,9 @@
       <c r="N146" s="10"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A147" s="107"/>
-      <c r="B147" s="95" t="s">
-        <v>39</v>
+      <c r="A147" s="123"/>
+      <c r="B147" s="93" t="s">
+        <v>90</v>
       </c>
       <c r="C147" s="8">
         <v>4</v>
@@ -8478,9 +8510,9 @@
       </c>
       <c r="N147" s="10"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A148" s="107"/>
-      <c r="B148" s="87" t="s">
+    <row r="148" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A148" s="123"/>
+      <c r="B148" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C148" s="11">
@@ -8519,9 +8551,9 @@
       </c>
       <c r="N148" s="10"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A149" s="107"/>
-      <c r="B149" s="87" t="s">
+    <row r="149" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A149" s="123"/>
+      <c r="B149" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C149" s="11">
@@ -8560,9 +8592,9 @@
       </c>
       <c r="N149" s="10"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A150" s="107"/>
-      <c r="B150" s="87" t="s">
+    <row r="150" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A150" s="123"/>
+      <c r="B150" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C150" s="11">
@@ -8601,9 +8633,9 @@
       </c>
       <c r="N150" s="10"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A151" s="107"/>
-      <c r="B151" s="87" t="s">
+    <row r="151" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A151" s="123"/>
+      <c r="B151" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C151" s="15">
@@ -8642,9 +8674,9 @@
       </c>
       <c r="N151" s="10"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A152" s="107"/>
-      <c r="B152" s="87" t="s">
+    <row r="152" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A152" s="123"/>
+      <c r="B152" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="15">
@@ -8683,10 +8715,10 @@
       </c>
       <c r="N152" s="10"/>
     </row>
-    <row r="153" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="108"/>
-      <c r="B153" s="88" t="s">
-        <v>85</v>
+    <row r="153" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="124"/>
+      <c r="B153" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C153" s="31">
         <v>5</v>
@@ -8725,11 +8757,11 @@
       <c r="N153" s="10"/>
     </row>
     <row r="154" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="106" t="s">
-        <v>57</v>
+      <c r="A154" s="122" t="s">
+        <v>56</v>
       </c>
       <c r="B154" s="84" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C154" s="28">
         <v>4</v>
@@ -8768,9 +8800,9 @@
       <c r="N154" s="10"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A155" s="107"/>
-      <c r="B155" s="98" t="s">
-        <v>54</v>
+      <c r="A155" s="123"/>
+      <c r="B155" s="143" t="s">
+        <v>95</v>
       </c>
       <c r="C155" s="11">
         <v>4</v>
@@ -8809,9 +8841,9 @@
       <c r="N155" s="10"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A156" s="107"/>
-      <c r="B156" s="98" t="s">
-        <v>55</v>
+      <c r="A156" s="123"/>
+      <c r="B156" s="143" t="s">
+        <v>96</v>
       </c>
       <c r="C156" s="11">
         <v>4</v>
@@ -8850,7 +8882,7 @@
       <c r="N156" s="10"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A157" s="107"/>
+      <c r="A157" s="123"/>
       <c r="B157" s="85" t="s">
         <v>17</v>
       </c>
@@ -8891,7 +8923,7 @@
       <c r="N157" s="10"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A158" s="107"/>
+      <c r="A158" s="123"/>
       <c r="B158" s="85" t="s">
         <v>26</v>
       </c>
@@ -8932,9 +8964,9 @@
       <c r="N158" s="10"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A159" s="107"/>
-      <c r="B159" s="85" t="s">
-        <v>27</v>
+      <c r="A159" s="123"/>
+      <c r="B159" s="139" t="s">
+        <v>89</v>
       </c>
       <c r="C159" s="11">
         <v>4</v>
@@ -8973,9 +9005,9 @@
       <c r="N159" s="10"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A160" s="107"/>
-      <c r="B160" s="85" t="s">
-        <v>18</v>
+      <c r="A160" s="123"/>
+      <c r="B160" s="139" t="s">
+        <v>88</v>
       </c>
       <c r="C160" s="11">
         <v>4</v>
@@ -9014,9 +9046,9 @@
       <c r="N160" s="10"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A161" s="107"/>
-      <c r="B161" s="95" t="s">
-        <v>39</v>
+      <c r="A161" s="123"/>
+      <c r="B161" s="93" t="s">
+        <v>90</v>
       </c>
       <c r="C161" s="8">
         <v>4</v>
@@ -9054,9 +9086,9 @@
       </c>
       <c r="N161" s="10"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A162" s="107"/>
-      <c r="B162" s="87" t="s">
+    <row r="162" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A162" s="123"/>
+      <c r="B162" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C162" s="8">
@@ -9095,9 +9127,9 @@
       </c>
       <c r="N162" s="10"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A163" s="107"/>
-      <c r="B163" s="87" t="s">
+    <row r="163" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A163" s="123"/>
+      <c r="B163" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C163" s="8">
@@ -9136,9 +9168,9 @@
       </c>
       <c r="N163" s="10"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A164" s="107"/>
-      <c r="B164" s="87" t="s">
+    <row r="164" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A164" s="123"/>
+      <c r="B164" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C164" s="8">
@@ -9178,9 +9210,9 @@
       <c r="N164" s="10"/>
     </row>
     <row r="165" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="108"/>
-      <c r="B165" s="88" t="s">
-        <v>85</v>
+      <c r="A165" s="124"/>
+      <c r="B165" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C165" s="31">
         <v>5</v>
@@ -9219,14 +9251,14 @@
       <c r="N165" s="10"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A166" s="106" t="s">
-        <v>58</v>
-      </c>
-      <c r="B166" s="96" t="s">
+      <c r="A166" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="B166" s="141" t="s">
+        <v>94</v>
+      </c>
+      <c r="C166" s="34" t="s">
         <v>48</v>
-      </c>
-      <c r="C166" s="34" t="s">
-        <v>49</v>
       </c>
       <c r="D166" s="50" t="s">
         <v>19</v>
@@ -9262,12 +9294,12 @@
       <c r="N166" s="10"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A167" s="107"/>
-      <c r="B167" s="97" t="s">
+      <c r="A167" s="123"/>
+      <c r="B167" s="95" t="s">
+        <v>49</v>
+      </c>
+      <c r="C167" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="C167" s="12" t="s">
-        <v>51</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>19</v>
@@ -9303,9 +9335,9 @@
       <c r="N167" s="10"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A168" s="107"/>
-      <c r="B168" s="97" t="s">
-        <v>43</v>
+      <c r="A168" s="123"/>
+      <c r="B168" s="142" t="s">
+        <v>91</v>
       </c>
       <c r="C168" s="11">
         <v>4</v>
@@ -9344,9 +9376,9 @@
       <c r="N168" s="10"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A169" s="107"/>
-      <c r="B169" s="97" t="s">
-        <v>45</v>
+      <c r="A169" s="123"/>
+      <c r="B169" s="142" t="s">
+        <v>93</v>
       </c>
       <c r="C169" s="11">
         <v>4</v>
@@ -9385,9 +9417,9 @@
       <c r="N169" s="10"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A170" s="107"/>
-      <c r="B170" s="98" t="s">
-        <v>53</v>
+      <c r="A170" s="123"/>
+      <c r="B170" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C170" s="11">
         <v>5</v>
@@ -9426,9 +9458,9 @@
       <c r="N170" s="10"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A171" s="107"/>
-      <c r="B171" s="98" t="s">
-        <v>54</v>
+      <c r="A171" s="123"/>
+      <c r="B171" s="143" t="s">
+        <v>95</v>
       </c>
       <c r="C171" s="11">
         <v>5</v>
@@ -9467,9 +9499,9 @@
       <c r="N171" s="10"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A172" s="107"/>
-      <c r="B172" s="98" t="s">
-        <v>55</v>
+      <c r="A172" s="123"/>
+      <c r="B172" s="143" t="s">
+        <v>96</v>
       </c>
       <c r="C172" s="11">
         <v>5</v>
@@ -9508,9 +9540,9 @@
       <c r="N172" s="10"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A173" s="107"/>
-      <c r="B173" s="98" t="s">
-        <v>56</v>
+      <c r="A173" s="123"/>
+      <c r="B173" s="143" t="s">
+        <v>97</v>
       </c>
       <c r="C173" s="11">
         <v>5</v>
@@ -9549,7 +9581,7 @@
       <c r="N173" s="10"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A174" s="107"/>
+      <c r="A174" s="123"/>
       <c r="B174" s="85" t="s">
         <v>16</v>
       </c>
@@ -9590,7 +9622,7 @@
       <c r="N174" s="10"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A175" s="107"/>
+      <c r="A175" s="123"/>
       <c r="B175" s="85" t="s">
         <v>17</v>
       </c>
@@ -9631,7 +9663,7 @@
       <c r="N175" s="10"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A176" s="107"/>
+      <c r="A176" s="123"/>
       <c r="B176" s="85" t="s">
         <v>26</v>
       </c>
@@ -9672,9 +9704,9 @@
       <c r="N176" s="10"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A177" s="107"/>
-      <c r="B177" s="85" t="s">
-        <v>27</v>
+      <c r="A177" s="123"/>
+      <c r="B177" s="139" t="s">
+        <v>89</v>
       </c>
       <c r="C177" s="11">
         <v>5</v>
@@ -9713,9 +9745,9 @@
       <c r="N177" s="10"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A178" s="107"/>
-      <c r="B178" s="85" t="s">
-        <v>18</v>
+      <c r="A178" s="123"/>
+      <c r="B178" s="139" t="s">
+        <v>88</v>
       </c>
       <c r="C178" s="11">
         <v>5</v>
@@ -9754,9 +9786,9 @@
       <c r="N178" s="10"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A179" s="107"/>
-      <c r="B179" s="85" t="s">
-        <v>39</v>
+      <c r="A179" s="123"/>
+      <c r="B179" s="139" t="s">
+        <v>90</v>
       </c>
       <c r="C179" s="11">
         <v>5</v>
@@ -9794,9 +9826,9 @@
       </c>
       <c r="N179" s="10"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A180" s="107"/>
-      <c r="B180" s="87" t="s">
+    <row r="180" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A180" s="123"/>
+      <c r="B180" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C180" s="11">
@@ -9835,9 +9867,9 @@
       </c>
       <c r="N180" s="10"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A181" s="107"/>
-      <c r="B181" s="87" t="s">
+    <row r="181" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A181" s="123"/>
+      <c r="B181" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C181" s="11">
@@ -9876,9 +9908,9 @@
       </c>
       <c r="N181" s="10"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A182" s="107"/>
-      <c r="B182" s="87" t="s">
+    <row r="182" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A182" s="123"/>
+      <c r="B182" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C182" s="11">
@@ -9917,10 +9949,10 @@
       </c>
       <c r="N182" s="10"/>
     </row>
-    <row r="183" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="108"/>
-      <c r="B183" s="88" t="s">
-        <v>85</v>
+    <row r="183" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="124"/>
+      <c r="B183" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C183" s="31">
         <v>6</v>
@@ -9959,11 +9991,11 @@
       <c r="N183" s="10"/>
     </row>
     <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="106" t="s">
-        <v>59</v>
-      </c>
-      <c r="B184" s="96" t="s">
-        <v>45</v>
+      <c r="A184" s="122" t="s">
+        <v>58</v>
+      </c>
+      <c r="B184" s="94" t="s">
+        <v>44</v>
       </c>
       <c r="C184" s="28">
         <v>4</v>
@@ -10002,9 +10034,9 @@
       <c r="N184" s="10"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A185" s="107"/>
-      <c r="B185" s="85" t="s">
-        <v>39</v>
+      <c r="A185" s="123"/>
+      <c r="B185" s="139" t="s">
+        <v>90</v>
       </c>
       <c r="C185" s="11">
         <v>6</v>
@@ -10042,9 +10074,9 @@
       </c>
       <c r="N185" s="10"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A186" s="107"/>
-      <c r="B186" s="87" t="s">
+    <row r="186" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A186" s="123"/>
+      <c r="B186" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C186" s="11">
@@ -10084,9 +10116,9 @@
       <c r="N186" s="10"/>
     </row>
     <row r="187" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="108"/>
-      <c r="B187" s="88" t="s">
-        <v>85</v>
+      <c r="A187" s="124"/>
+      <c r="B187" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C187" s="31">
         <v>6</v>
@@ -10125,11 +10157,11 @@
       <c r="N187" s="10"/>
     </row>
     <row r="188" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="106" t="s">
-        <v>60</v>
-      </c>
-      <c r="B188" s="96" t="s">
-        <v>45</v>
+      <c r="A188" s="122" t="s">
+        <v>59</v>
+      </c>
+      <c r="B188" s="94" t="s">
+        <v>44</v>
       </c>
       <c r="C188" s="28">
         <v>4</v>
@@ -10168,9 +10200,9 @@
       <c r="N188" s="10"/>
     </row>
     <row r="189" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="107"/>
-      <c r="B189" s="98" t="s">
-        <v>52</v>
+      <c r="A189" s="123"/>
+      <c r="B189" s="96" t="s">
+        <v>51</v>
       </c>
       <c r="C189" s="11">
         <v>5</v>
@@ -10209,9 +10241,9 @@
       <c r="N189" s="10"/>
     </row>
     <row r="190" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="107"/>
-      <c r="B190" s="98" t="s">
-        <v>53</v>
+      <c r="A190" s="123"/>
+      <c r="B190" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C190" s="11">
         <v>5</v>
@@ -10250,9 +10282,9 @@
       <c r="N190" s="10"/>
     </row>
     <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="107"/>
-      <c r="B191" s="98" t="s">
-        <v>54</v>
+      <c r="A191" s="123"/>
+      <c r="B191" s="96" t="s">
+        <v>53</v>
       </c>
       <c r="C191" s="11">
         <v>5</v>
@@ -10291,9 +10323,9 @@
       <c r="N191" s="10"/>
     </row>
     <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="107"/>
-      <c r="B192" s="98" t="s">
-        <v>55</v>
+      <c r="A192" s="123"/>
+      <c r="B192" s="96" t="s">
+        <v>54</v>
       </c>
       <c r="C192" s="11">
         <v>5</v>
@@ -10332,9 +10364,9 @@
       <c r="N192" s="10"/>
     </row>
     <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="107"/>
-      <c r="B193" s="98" t="s">
-        <v>56</v>
+      <c r="A193" s="123"/>
+      <c r="B193" s="96" t="s">
+        <v>55</v>
       </c>
       <c r="C193" s="11">
         <v>5</v>
@@ -10373,7 +10405,7 @@
       <c r="N193" s="10"/>
     </row>
     <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="107"/>
+      <c r="A194" s="123"/>
       <c r="B194" s="85" t="s">
         <v>16</v>
       </c>
@@ -10414,7 +10446,7 @@
       <c r="N194" s="10"/>
     </row>
     <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="107"/>
+      <c r="A195" s="123"/>
       <c r="B195" s="85" t="s">
         <v>17</v>
       </c>
@@ -10455,7 +10487,7 @@
       <c r="N195" s="10"/>
     </row>
     <row r="196" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="107"/>
+      <c r="A196" s="123"/>
       <c r="B196" s="85" t="s">
         <v>26</v>
       </c>
@@ -10496,7 +10528,7 @@
       <c r="N196" s="10"/>
     </row>
     <row r="197" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="107"/>
+      <c r="A197" s="123"/>
       <c r="B197" s="85" t="s">
         <v>27</v>
       </c>
@@ -10537,7 +10569,7 @@
       <c r="N197" s="10"/>
     </row>
     <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="107"/>
+      <c r="A198" s="123"/>
       <c r="B198" s="85" t="s">
         <v>18</v>
       </c>
@@ -10578,7 +10610,7 @@
       <c r="N198" s="10"/>
     </row>
     <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="107"/>
+      <c r="A199" s="123"/>
       <c r="B199" s="85" t="s">
         <v>39</v>
       </c>
@@ -10618,9 +10650,9 @@
       </c>
       <c r="N199" s="10"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A200" s="107"/>
-      <c r="B200" s="87" t="s">
+    <row r="200" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A200" s="123"/>
+      <c r="B200" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C200" s="11">
@@ -10659,9 +10691,9 @@
       </c>
       <c r="N200" s="10"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A201" s="107"/>
-      <c r="B201" s="87" t="s">
+    <row r="201" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A201" s="123"/>
+      <c r="B201" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C201" s="11">
@@ -10700,9 +10732,9 @@
       </c>
       <c r="N201" s="10"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A202" s="107"/>
-      <c r="B202" s="87" t="s">
+    <row r="202" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A202" s="123"/>
+      <c r="B202" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C202" s="15">
@@ -10741,9 +10773,9 @@
       </c>
       <c r="N202" s="10"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A203" s="107"/>
-      <c r="B203" s="87" t="s">
+    <row r="203" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A203" s="123"/>
+      <c r="B203" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C203" s="15">
@@ -10783,9 +10815,9 @@
       <c r="N203" s="10"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A204" s="107"/>
-      <c r="B204" s="99" t="s">
-        <v>85</v>
+      <c r="A204" s="123"/>
+      <c r="B204" s="97" t="s">
+        <v>82</v>
       </c>
       <c r="C204" s="11">
         <v>6</v>
@@ -10824,9 +10856,9 @@
       <c r="N204" s="10"/>
     </row>
     <row r="205" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="108"/>
-      <c r="B205" s="100" t="s">
-        <v>88</v>
+      <c r="A205" s="124"/>
+      <c r="B205" s="98" t="s">
+        <v>85</v>
       </c>
       <c r="C205" s="31">
         <v>6</v>
@@ -10865,11 +10897,11 @@
       <c r="N205" s="10"/>
     </row>
     <row r="206" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="106" t="s">
-        <v>61</v>
+      <c r="A206" s="122" t="s">
+        <v>60</v>
       </c>
       <c r="B206" s="84" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C206" s="28">
         <v>4</v>
@@ -10908,9 +10940,9 @@
       <c r="N206" s="10"/>
     </row>
     <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="107"/>
-      <c r="B207" s="98" t="s">
-        <v>54</v>
+      <c r="A207" s="123"/>
+      <c r="B207" s="96" t="s">
+        <v>53</v>
       </c>
       <c r="C207" s="11">
         <v>4</v>
@@ -10949,9 +10981,9 @@
       <c r="N207" s="10"/>
     </row>
     <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="107"/>
-      <c r="B208" s="98" t="s">
-        <v>55</v>
+      <c r="A208" s="123"/>
+      <c r="B208" s="96" t="s">
+        <v>54</v>
       </c>
       <c r="C208" s="11">
         <v>4</v>
@@ -10990,9 +11022,9 @@
       <c r="N208" s="10"/>
     </row>
     <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="107"/>
-      <c r="B209" s="98" t="s">
-        <v>56</v>
+      <c r="A209" s="123"/>
+      <c r="B209" s="96" t="s">
+        <v>55</v>
       </c>
       <c r="C209" s="11">
         <v>4</v>
@@ -11031,7 +11063,7 @@
       <c r="N209" s="10"/>
     </row>
     <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="107"/>
+      <c r="A210" s="123"/>
       <c r="B210" s="85" t="s">
         <v>16</v>
       </c>
@@ -11072,7 +11104,7 @@
       <c r="N210" s="10"/>
     </row>
     <row r="211" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="107"/>
+      <c r="A211" s="123"/>
       <c r="B211" s="85" t="s">
         <v>17</v>
       </c>
@@ -11113,7 +11145,7 @@
       <c r="N211" s="10"/>
     </row>
     <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="107"/>
+      <c r="A212" s="123"/>
       <c r="B212" s="85" t="s">
         <v>26</v>
       </c>
@@ -11154,7 +11186,7 @@
       <c r="N212" s="10"/>
     </row>
     <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="107"/>
+      <c r="A213" s="123"/>
       <c r="B213" s="85" t="s">
         <v>27</v>
       </c>
@@ -11195,7 +11227,7 @@
       <c r="N213" s="10"/>
     </row>
     <row r="214" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="107"/>
+      <c r="A214" s="123"/>
       <c r="B214" s="85" t="s">
         <v>18</v>
       </c>
@@ -11236,7 +11268,7 @@
       <c r="N214" s="10"/>
     </row>
     <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="107"/>
+      <c r="A215" s="123"/>
       <c r="B215" s="85" t="s">
         <v>39</v>
       </c>
@@ -11276,9 +11308,9 @@
       </c>
       <c r="N215" s="10"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A216" s="107"/>
-      <c r="B216" s="87" t="s">
+    <row r="216" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A216" s="123"/>
+      <c r="B216" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C216" s="11">
@@ -11317,9 +11349,9 @@
       </c>
       <c r="N216" s="10"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A217" s="107"/>
-      <c r="B217" s="87" t="s">
+    <row r="217" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A217" s="123"/>
+      <c r="B217" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C217" s="11">
@@ -11358,9 +11390,9 @@
       </c>
       <c r="N217" s="10"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A218" s="107"/>
-      <c r="B218" s="87" t="s">
+    <row r="218" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A218" s="123"/>
+      <c r="B218" s="86" t="s">
         <v>22</v>
       </c>
       <c r="C218" s="11">
@@ -11399,9 +11431,9 @@
       </c>
       <c r="N218" s="10"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A219" s="107"/>
-      <c r="B219" s="87" t="s">
+    <row r="219" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A219" s="123"/>
+      <c r="B219" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C219" s="15">
@@ -11440,9 +11472,9 @@
       </c>
       <c r="N219" s="10"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A220" s="107"/>
-      <c r="B220" s="87" t="s">
+    <row r="220" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A220" s="123"/>
+      <c r="B220" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C220" s="15">
@@ -11481,97 +11513,97 @@
       </c>
       <c r="N220" s="10"/>
     </row>
-    <row r="221" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="107"/>
-      <c r="B221" s="99" t="s">
-        <v>85</v>
-      </c>
-      <c r="C221" s="11">
+    <row r="221" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="124"/>
+      <c r="B221" s="87" t="s">
+        <v>82</v>
+      </c>
+      <c r="C221" s="31">
         <v>7</v>
       </c>
-      <c r="D221" s="3" t="s">
+      <c r="D221" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="E221" s="37">
+      <c r="E221" s="42">
         <v>11.2</v>
       </c>
-      <c r="F221" s="40">
+      <c r="F221" s="43">
         <v>10.666</v>
       </c>
-      <c r="G221" s="37">
+      <c r="G221" s="42">
         <v>11.2</v>
       </c>
-      <c r="H221" s="37">
+      <c r="H221" s="42">
         <v>10.032999999999999</v>
       </c>
-      <c r="I221" s="37">
+      <c r="I221" s="42">
         <v>11.032999999999999</v>
       </c>
-      <c r="J221" s="37">
+      <c r="J221" s="42">
         <v>10.866</v>
       </c>
-      <c r="K221" s="23" cm="1">
+      <c r="K221" s="52" cm="1">
         <f t="array" ref="K221">SUM(E221:J221)</f>
         <v>64.998000000000005</v>
       </c>
-      <c r="L221" s="11">
+      <c r="L221" s="31">
         <v>1</v>
       </c>
-      <c r="M221" s="78">
+      <c r="M221" s="79">
         <v>24</v>
       </c>
       <c r="N221" s="10"/>
     </row>
     <row r="222" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="B222" s="133" t="s">
-        <v>48</v>
-      </c>
-      <c r="C222" s="130" t="s">
-        <v>51</v>
-      </c>
-      <c r="D222" s="134" t="s">
+      <c r="A222" s="122" t="s">
+        <v>61</v>
+      </c>
+      <c r="B222" s="94" t="s">
+        <v>47</v>
+      </c>
+      <c r="C222" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D222" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E222" s="120">
+      <c r="E222" s="41">
         <v>6.9</v>
       </c>
-      <c r="F222" s="120">
+      <c r="F222" s="41">
         <v>9.1</v>
       </c>
-      <c r="G222" s="120">
+      <c r="G222" s="41">
         <v>9.1</v>
       </c>
-      <c r="H222" s="120">
+      <c r="H222" s="41">
         <v>9.1</v>
       </c>
-      <c r="I222" s="120">
+      <c r="I222" s="41">
         <v>8</v>
       </c>
-      <c r="J222" s="120">
+      <c r="J222" s="41">
         <v>8.4</v>
       </c>
-      <c r="K222" s="121" cm="1">
+      <c r="K222" s="30" cm="1">
         <f t="array" ref="K222">SUM(E222:J222)</f>
         <v>50.6</v>
       </c>
-      <c r="L222" s="118">
+      <c r="L222" s="28">
         <v>2</v>
       </c>
-      <c r="M222" s="122">
+      <c r="M222" s="77">
         <v>4</v>
       </c>
       <c r="N222" s="10"/>
     </row>
     <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="131"/>
-      <c r="B223" s="97" t="s">
-        <v>50</v>
+      <c r="A223" s="123"/>
+      <c r="B223" s="95" t="s">
+        <v>49</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>34</v>
@@ -11601,18 +11633,18 @@
       <c r="L223" s="11">
         <v>1</v>
       </c>
-      <c r="M223" s="124">
+      <c r="M223" s="78">
         <v>1</v>
       </c>
       <c r="N223" s="10"/>
     </row>
     <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="131"/>
-      <c r="B224" s="97" t="s">
-        <v>64</v>
+      <c r="A224" s="123"/>
+      <c r="B224" s="95" t="s">
+        <v>63</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D224" s="5" t="s">
         <v>34</v>
@@ -11642,14 +11674,14 @@
       <c r="L224" s="11">
         <v>12</v>
       </c>
-      <c r="M224" s="124">
+      <c r="M224" s="78">
         <v>26</v>
       </c>
       <c r="N224" s="10"/>
     </row>
     <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="131"/>
-      <c r="B225" s="97" t="s">
+      <c r="A225" s="123"/>
+      <c r="B225" s="95" t="s">
         <v>43</v>
       </c>
       <c r="C225" s="11">
@@ -11683,15 +11715,15 @@
       <c r="L225" s="11">
         <v>4</v>
       </c>
-      <c r="M225" s="124">
+      <c r="M225" s="78">
         <v>10</v>
       </c>
       <c r="N225" s="10"/>
     </row>
     <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="131"/>
-      <c r="B226" s="97" t="s">
-        <v>45</v>
+      <c r="A226" s="123"/>
+      <c r="B226" s="95" t="s">
+        <v>44</v>
       </c>
       <c r="C226" s="11">
         <v>4</v>
@@ -11724,15 +11756,15 @@
       <c r="L226" s="11">
         <v>8</v>
       </c>
-      <c r="M226" s="124">
+      <c r="M226" s="78">
         <v>48</v>
       </c>
       <c r="N226" s="10"/>
     </row>
     <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="131"/>
-      <c r="B227" s="98" t="s">
-        <v>52</v>
+      <c r="A227" s="123"/>
+      <c r="B227" s="96" t="s">
+        <v>51</v>
       </c>
       <c r="C227" s="11">
         <v>5</v>
@@ -11765,15 +11797,15 @@
       <c r="L227" s="11">
         <v>1</v>
       </c>
-      <c r="M227" s="124">
+      <c r="M227" s="78">
         <v>4</v>
       </c>
       <c r="N227" s="10"/>
     </row>
     <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="131"/>
-      <c r="B228" s="98" t="s">
-        <v>53</v>
+      <c r="A228" s="123"/>
+      <c r="B228" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C228" s="11">
         <v>5</v>
@@ -11806,15 +11838,15 @@
       <c r="L228" s="11">
         <v>1</v>
       </c>
-      <c r="M228" s="124">
+      <c r="M228" s="78">
         <v>3</v>
       </c>
       <c r="N228" s="10"/>
     </row>
     <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="131"/>
-      <c r="B229" s="98" t="s">
-        <v>54</v>
+      <c r="A229" s="123"/>
+      <c r="B229" s="96" t="s">
+        <v>53</v>
       </c>
       <c r="C229" s="11">
         <v>5</v>
@@ -11847,15 +11879,15 @@
       <c r="L229" s="11">
         <v>1</v>
       </c>
-      <c r="M229" s="124">
+      <c r="M229" s="78">
         <v>7</v>
       </c>
       <c r="N229" s="10"/>
     </row>
     <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="131"/>
-      <c r="B230" s="98" t="s">
-        <v>55</v>
+      <c r="A230" s="123"/>
+      <c r="B230" s="96" t="s">
+        <v>54</v>
       </c>
       <c r="C230" s="11">
         <v>5</v>
@@ -11888,15 +11920,15 @@
       <c r="L230" s="11">
         <v>2</v>
       </c>
-      <c r="M230" s="124">
+      <c r="M230" s="78">
         <v>14</v>
       </c>
       <c r="N230" s="10"/>
     </row>
     <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="131"/>
-      <c r="B231" s="98" t="s">
-        <v>56</v>
+      <c r="A231" s="123"/>
+      <c r="B231" s="96" t="s">
+        <v>55</v>
       </c>
       <c r="C231" s="11">
         <v>5</v>
@@ -11929,13 +11961,13 @@
       <c r="L231" s="11">
         <v>8</v>
       </c>
-      <c r="M231" s="124">
+      <c r="M231" s="78">
         <v>32</v>
       </c>
       <c r="N231" s="10"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A232" s="131"/>
+      <c r="A232" s="123"/>
       <c r="B232" s="85" t="s">
         <v>16</v>
       </c>
@@ -11970,13 +12002,13 @@
       <c r="L232" s="11">
         <v>46</v>
       </c>
-      <c r="M232" s="124">
+      <c r="M232" s="78">
         <v>53</v>
       </c>
       <c r="N232" s="10"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A233" s="131"/>
+      <c r="A233" s="123"/>
       <c r="B233" s="85" t="s">
         <v>17</v>
       </c>
@@ -12011,13 +12043,13 @@
       <c r="L233" s="11">
         <v>3</v>
       </c>
-      <c r="M233" s="124">
+      <c r="M233" s="78">
         <v>4</v>
       </c>
       <c r="N233" s="10"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A234" s="131"/>
+      <c r="A234" s="123"/>
       <c r="B234" s="85" t="s">
         <v>26</v>
       </c>
@@ -12052,15 +12084,15 @@
       <c r="L234" s="11">
         <v>2</v>
       </c>
-      <c r="M234" s="124">
+      <c r="M234" s="78">
         <v>2</v>
       </c>
       <c r="N234" s="10"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A235" s="131"/>
-      <c r="B235" s="85" t="s">
-        <v>18</v>
+      <c r="A235" s="123"/>
+      <c r="B235" s="139" t="s">
+        <v>88</v>
       </c>
       <c r="C235" s="11">
         <v>7</v>
@@ -12093,15 +12125,15 @@
       <c r="L235" s="11">
         <v>3</v>
       </c>
-      <c r="M235" s="124">
+      <c r="M235" s="78">
         <v>4</v>
       </c>
       <c r="N235" s="10"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A236" s="131"/>
-      <c r="B236" s="85" t="s">
-        <v>39</v>
+      <c r="A236" s="123"/>
+      <c r="B236" s="139" t="s">
+        <v>90</v>
       </c>
       <c r="C236" s="11">
         <v>7</v>
@@ -12134,14 +12166,14 @@
       <c r="L236" s="11">
         <v>10</v>
       </c>
-      <c r="M236" s="124">
+      <c r="M236" s="78">
         <v>24</v>
       </c>
       <c r="N236" s="10"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A237" s="131"/>
-      <c r="B237" s="87" t="s">
+    <row r="237" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A237" s="123"/>
+      <c r="B237" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C237" s="11">
@@ -12175,14 +12207,14 @@
       <c r="L237" s="11">
         <v>1</v>
       </c>
-      <c r="M237" s="124">
+      <c r="M237" s="78">
         <v>2</v>
       </c>
       <c r="N237" s="10"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A238" s="131"/>
-      <c r="B238" s="87" t="s">
+    <row r="238" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A238" s="123"/>
+      <c r="B238" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C238" s="11">
@@ -12216,14 +12248,14 @@
       <c r="L238" s="11">
         <v>1</v>
       </c>
-      <c r="M238" s="124">
+      <c r="M238" s="78">
         <v>3</v>
       </c>
       <c r="N238" s="10"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A239" s="131"/>
-      <c r="B239" s="87" t="s">
+    <row r="239" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A239" s="123"/>
+      <c r="B239" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C239" s="15">
@@ -12257,14 +12289,14 @@
       <c r="L239" s="11">
         <v>2</v>
       </c>
-      <c r="M239" s="124">
+      <c r="M239" s="78">
         <v>4</v>
       </c>
       <c r="N239" s="10"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A240" s="131"/>
-      <c r="B240" s="87" t="s">
+    <row r="240" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A240" s="123"/>
+      <c r="B240" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C240" s="15">
@@ -12298,61 +12330,61 @@
       <c r="L240" s="11">
         <v>2</v>
       </c>
-      <c r="M240" s="124">
+      <c r="M240" s="78">
         <v>3</v>
       </c>
       <c r="N240" s="10"/>
     </row>
     <row r="241" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="131"/>
-      <c r="B241" s="99" t="s">
-        <v>85</v>
-      </c>
-      <c r="C241" s="19">
+      <c r="A241" s="124"/>
+      <c r="B241" s="87" t="s">
+        <v>82</v>
+      </c>
+      <c r="C241" s="31">
         <v>7</v>
       </c>
-      <c r="D241" s="135" t="s">
+      <c r="D241" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="E241" s="126">
+      <c r="E241" s="42">
         <v>10.666</v>
       </c>
-      <c r="F241" s="126">
+      <c r="F241" s="42">
         <v>10.233000000000001</v>
       </c>
-      <c r="G241" s="126">
+      <c r="G241" s="42">
         <v>11.1</v>
       </c>
-      <c r="H241" s="126">
+      <c r="H241" s="42">
         <v>9</v>
       </c>
-      <c r="I241" s="126">
+      <c r="I241" s="42">
         <v>9.8000000000000007</v>
       </c>
-      <c r="J241" s="126">
+      <c r="J241" s="42">
         <v>8.6</v>
       </c>
-      <c r="K241" s="136" cm="1">
+      <c r="K241" s="144" cm="1">
         <f t="array" ref="K241">SUM(E241:J241)</f>
         <v>59.399000000000008</v>
       </c>
-      <c r="L241" s="19">
+      <c r="L241" s="31">
         <v>8</v>
       </c>
-      <c r="M241" s="128">
+      <c r="M241" s="79">
         <v>23</v>
       </c>
       <c r="N241" s="10"/>
     </row>
     <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="129" t="s">
+      <c r="A242" s="131" t="s">
+        <v>64</v>
+      </c>
+      <c r="B242" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="B242" s="137" t="s">
-        <v>66</v>
-      </c>
       <c r="C242" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>15</v>
@@ -12382,18 +12414,18 @@
       <c r="L242" s="11">
         <v>1</v>
       </c>
-      <c r="M242" s="124">
+      <c r="M242" s="109">
         <v>5</v>
       </c>
       <c r="N242" s="10"/>
     </row>
     <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="131"/>
-      <c r="B243" s="138" t="s">
-        <v>67</v>
+      <c r="B243" s="113" t="s">
+        <v>66</v>
       </c>
       <c r="C243" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>15</v>
@@ -12423,15 +12455,15 @@
       <c r="L243" s="11">
         <v>1</v>
       </c>
-      <c r="M243" s="124">
+      <c r="M243" s="109">
         <v>6</v>
       </c>
       <c r="N243" s="10"/>
     </row>
     <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="131"/>
-      <c r="B244" s="138" t="s">
-        <v>64</v>
+      <c r="B244" s="113" t="s">
+        <v>63</v>
       </c>
       <c r="C244" s="11">
         <v>5</v>
@@ -12464,14 +12496,14 @@
       <c r="L244" s="11">
         <v>4</v>
       </c>
-      <c r="M244" s="124">
+      <c r="M244" s="109">
         <v>11</v>
       </c>
       <c r="N244" s="10"/>
     </row>
     <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="131"/>
-      <c r="B245" s="138" t="s">
+      <c r="B245" s="113" t="s">
         <v>43</v>
       </c>
       <c r="C245" s="11">
@@ -12505,15 +12537,15 @@
       <c r="L245" s="11">
         <v>3</v>
       </c>
-      <c r="M245" s="124">
+      <c r="M245" s="109">
         <v>4</v>
       </c>
       <c r="N245" s="10"/>
     </row>
     <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="131"/>
-      <c r="B246" s="138" t="s">
-        <v>45</v>
+      <c r="B246" s="113" t="s">
+        <v>44</v>
       </c>
       <c r="C246" s="11">
         <v>6</v>
@@ -12546,15 +12578,15 @@
       <c r="L246" s="11">
         <v>17</v>
       </c>
-      <c r="M246" s="124">
+      <c r="M246" s="109">
         <v>23</v>
       </c>
       <c r="N246" s="10"/>
     </row>
     <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="131"/>
-      <c r="B247" s="138" t="s">
-        <v>68</v>
+      <c r="B247" s="113" t="s">
+        <v>67</v>
       </c>
       <c r="C247" s="11">
         <v>6</v>
@@ -12587,15 +12619,15 @@
       <c r="L247" s="11">
         <v>16</v>
       </c>
-      <c r="M247" s="124">
+      <c r="M247" s="109">
         <v>23</v>
       </c>
       <c r="N247" s="10"/>
     </row>
     <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="131"/>
-      <c r="B248" s="139" t="s">
-        <v>53</v>
+      <c r="B248" s="114" t="s">
+        <v>52</v>
       </c>
       <c r="C248" s="11">
         <v>6</v>
@@ -12628,15 +12660,15 @@
       <c r="L248" s="11">
         <v>1</v>
       </c>
-      <c r="M248" s="124">
+      <c r="M248" s="109">
         <v>1</v>
       </c>
       <c r="N248" s="10"/>
     </row>
     <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="131"/>
-      <c r="B249" s="139" t="s">
-        <v>54</v>
+      <c r="B249" s="114" t="s">
+        <v>53</v>
       </c>
       <c r="C249" s="11">
         <v>6</v>
@@ -12669,15 +12701,15 @@
       <c r="L249" s="11">
         <v>4</v>
       </c>
-      <c r="M249" s="124">
+      <c r="M249" s="109">
         <v>10</v>
       </c>
       <c r="N249" s="10"/>
     </row>
     <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="131"/>
-      <c r="B250" s="139" t="s">
-        <v>55</v>
+      <c r="B250" s="114" t="s">
+        <v>54</v>
       </c>
       <c r="C250" s="11">
         <v>6</v>
@@ -12710,15 +12742,15 @@
       <c r="L250" s="11">
         <v>3</v>
       </c>
-      <c r="M250" s="124">
+      <c r="M250" s="109">
         <v>3</v>
       </c>
       <c r="N250" s="10"/>
     </row>
     <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="131"/>
-      <c r="B251" s="139" t="s">
-        <v>56</v>
+      <c r="B251" s="114" t="s">
+        <v>55</v>
       </c>
       <c r="C251" s="11">
         <v>6</v>
@@ -12751,15 +12783,15 @@
       <c r="L251" s="11">
         <v>7</v>
       </c>
-      <c r="M251" s="124">
+      <c r="M251" s="109">
         <v>24</v>
       </c>
       <c r="N251" s="10"/>
     </row>
     <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="131"/>
-      <c r="B252" s="139" t="s">
-        <v>69</v>
+      <c r="B252" s="114" t="s">
+        <v>68</v>
       </c>
       <c r="C252" s="11">
         <v>6</v>
@@ -12792,14 +12824,14 @@
       <c r="L252" s="11">
         <v>7</v>
       </c>
-      <c r="M252" s="124">
+      <c r="M252" s="109">
         <v>22</v>
       </c>
       <c r="N252" s="10"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253" s="131"/>
-      <c r="B253" s="140" t="s">
+      <c r="B253" s="115" t="s">
         <v>17</v>
       </c>
       <c r="C253" s="11">
@@ -12833,14 +12865,14 @@
       <c r="L253" s="11">
         <v>1</v>
       </c>
-      <c r="M253" s="124">
+      <c r="M253" s="109">
         <v>3</v>
       </c>
       <c r="N253" s="10"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254" s="131"/>
-      <c r="B254" s="140" t="s">
+      <c r="B254" s="115" t="s">
         <v>26</v>
       </c>
       <c r="C254" s="11">
@@ -12874,15 +12906,15 @@
       <c r="L254" s="11">
         <v>4</v>
       </c>
-      <c r="M254" s="124">
+      <c r="M254" s="109">
         <v>5</v>
       </c>
       <c r="N254" s="10"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255" s="131"/>
-      <c r="B255" s="140" t="s">
-        <v>27</v>
+      <c r="B255" s="145" t="s">
+        <v>89</v>
       </c>
       <c r="C255" s="11">
         <v>8</v>
@@ -12915,15 +12947,15 @@
       <c r="L255" s="11">
         <v>7</v>
       </c>
-      <c r="M255" s="124">
+      <c r="M255" s="109">
         <v>15</v>
       </c>
       <c r="N255" s="10"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256" s="131"/>
-      <c r="B256" s="140" t="s">
-        <v>18</v>
+      <c r="B256" s="145" t="s">
+        <v>88</v>
       </c>
       <c r="C256" s="11">
         <v>8</v>
@@ -12956,15 +12988,15 @@
       <c r="L256" s="11">
         <v>3</v>
       </c>
-      <c r="M256" s="124">
+      <c r="M256" s="109">
         <v>9</v>
       </c>
       <c r="N256" s="10"/>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" s="131"/>
-      <c r="B257" s="140" t="s">
-        <v>39</v>
+      <c r="B257" s="145" t="s">
+        <v>90</v>
       </c>
       <c r="C257" s="11">
         <v>8</v>
@@ -12997,15 +13029,15 @@
       <c r="L257" s="11">
         <v>13</v>
       </c>
-      <c r="M257" s="124">
+      <c r="M257" s="109">
         <v>31</v>
       </c>
       <c r="N257" s="10"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A258" s="131"/>
-      <c r="B258" s="141" t="s">
-        <v>70</v>
+      <c r="B258" s="116" t="s">
+        <v>69</v>
       </c>
       <c r="C258" s="11">
         <v>8</v>
@@ -13038,14 +13070,14 @@
       <c r="L258" s="11">
         <v>14</v>
       </c>
-      <c r="M258" s="124">
+      <c r="M258" s="109">
         <v>28</v>
       </c>
       <c r="N258" s="10"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="131"/>
-      <c r="B259" s="142" t="s">
+      <c r="B259" s="117" t="s">
         <v>20</v>
       </c>
       <c r="C259" s="11">
@@ -13079,14 +13111,14 @@
       <c r="L259" s="11">
         <v>1</v>
       </c>
-      <c r="M259" s="124">
+      <c r="M259" s="109">
         <v>4</v>
       </c>
       <c r="N259" s="10"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A260" s="131"/>
-      <c r="B260" s="142" t="s">
+      <c r="B260" s="117" t="s">
         <v>21</v>
       </c>
       <c r="C260" s="11">
@@ -13120,14 +13152,14 @@
       <c r="L260" s="11">
         <v>2</v>
       </c>
-      <c r="M260" s="124">
+      <c r="M260" s="109">
         <v>5</v>
       </c>
       <c r="N260" s="10"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A261" s="131"/>
-      <c r="B261" s="142" t="s">
+      <c r="B261" s="117" t="s">
         <v>23</v>
       </c>
       <c r="C261" s="15">
@@ -13161,14 +13193,14 @@
       <c r="L261" s="11">
         <v>1</v>
       </c>
-      <c r="M261" s="124">
+      <c r="M261" s="109">
         <v>1</v>
       </c>
       <c r="N261" s="10"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A262" s="131"/>
-      <c r="B262" s="142" t="s">
+      <c r="B262" s="117" t="s">
         <v>24</v>
       </c>
       <c r="C262" s="15">
@@ -13202,15 +13234,15 @@
       <c r="L262" s="11">
         <v>1</v>
       </c>
-      <c r="M262" s="124">
+      <c r="M262" s="109">
         <v>3</v>
       </c>
       <c r="N262" s="10"/>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263" s="131"/>
-      <c r="B263" s="143" t="s">
-        <v>85</v>
+      <c r="B263" s="118" t="s">
+        <v>82</v>
       </c>
       <c r="C263" s="11">
         <v>8</v>
@@ -13242,15 +13274,15 @@
       <c r="L263" s="11">
         <v>14</v>
       </c>
-      <c r="M263" s="124">
+      <c r="M263" s="109">
         <v>42</v>
       </c>
       <c r="N263" s="10"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A264" s="131"/>
-      <c r="B264" s="144" t="s">
-        <v>88</v>
+      <c r="B264" s="119" t="s">
+        <v>85</v>
       </c>
       <c r="C264" s="11">
         <v>8</v>
@@ -13283,15 +13315,15 @@
       <c r="L264" s="11">
         <v>12</v>
       </c>
-      <c r="M264" s="124">
+      <c r="M264" s="109">
         <v>37</v>
       </c>
       <c r="N264" s="10"/>
     </row>
     <row r="265" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A265" s="132"/>
-      <c r="B265" s="145" t="s">
-        <v>89</v>
+      <c r="B265" s="120" t="s">
+        <v>86</v>
       </c>
       <c r="C265" s="19">
         <v>8</v>
@@ -13299,37 +13331,37 @@
       <c r="D265" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E265" s="126">
+      <c r="E265" s="110">
         <v>11.7</v>
       </c>
-      <c r="F265" s="126"/>
-      <c r="G265" s="126">
+      <c r="F265" s="110"/>
+      <c r="G265" s="110">
         <v>11.233000000000001</v>
       </c>
-      <c r="H265" s="126"/>
-      <c r="I265" s="126"/>
-      <c r="J265" s="126"/>
-      <c r="K265" s="127">
+      <c r="H265" s="110"/>
+      <c r="I265" s="110"/>
+      <c r="J265" s="110"/>
+      <c r="K265" s="111">
         <f>SUM(E265:J265)</f>
         <v>22.933</v>
       </c>
       <c r="L265" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="M265" s="128">
+        <v>87</v>
+      </c>
+      <c r="M265" s="112">
         <v>8</v>
       </c>
       <c r="N265" s="10"/>
     </row>
     <row r="266" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A266" s="107" t="s">
-        <v>86</v>
-      </c>
-      <c r="B266" s="97" t="s">
-        <v>66</v>
+      <c r="A266" s="123" t="s">
+        <v>83</v>
+      </c>
+      <c r="B266" s="95" t="s">
+        <v>65</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D266" s="3" t="s">
         <v>19</v>
@@ -13365,12 +13397,12 @@
       <c r="N266" s="10"/>
     </row>
     <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A267" s="107"/>
-      <c r="B267" s="97" t="s">
-        <v>67</v>
+      <c r="A267" s="123"/>
+      <c r="B267" s="95" t="s">
+        <v>66</v>
       </c>
       <c r="C267" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>19</v>
@@ -13406,12 +13438,12 @@
       <c r="N267" s="10"/>
     </row>
     <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A268" s="107"/>
-      <c r="B268" s="97" t="s">
-        <v>64</v>
+      <c r="A268" s="123"/>
+      <c r="B268" s="95" t="s">
+        <v>63</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>19</v>
@@ -13447,8 +13479,8 @@
       <c r="N268" s="10"/>
     </row>
     <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A269" s="107"/>
-      <c r="B269" s="97" t="s">
+      <c r="A269" s="123"/>
+      <c r="B269" s="95" t="s">
         <v>43</v>
       </c>
       <c r="C269" s="11">
@@ -13488,9 +13520,9 @@
       <c r="N269" s="10"/>
     </row>
     <row r="270" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="107"/>
-      <c r="B270" s="97" t="s">
-        <v>45</v>
+      <c r="A270" s="123"/>
+      <c r="B270" s="95" t="s">
+        <v>44</v>
       </c>
       <c r="C270" s="11">
         <v>6</v>
@@ -13529,9 +13561,9 @@
       <c r="N270" s="10"/>
     </row>
     <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="107"/>
-      <c r="B271" s="97" t="s">
-        <v>68</v>
+      <c r="A271" s="123"/>
+      <c r="B271" s="95" t="s">
+        <v>67</v>
       </c>
       <c r="C271" s="11">
         <v>6</v>
@@ -13570,9 +13602,9 @@
       <c r="N271" s="10"/>
     </row>
     <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="107"/>
-      <c r="B272" s="98" t="s">
-        <v>53</v>
+      <c r="A272" s="123"/>
+      <c r="B272" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C272" s="11">
         <v>8</v>
@@ -13611,9 +13643,9 @@
       <c r="N272" s="10"/>
     </row>
     <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A273" s="107"/>
-      <c r="B273" s="98" t="s">
-        <v>54</v>
+      <c r="A273" s="123"/>
+      <c r="B273" s="96" t="s">
+        <v>53</v>
       </c>
       <c r="C273" s="11">
         <v>8</v>
@@ -13652,9 +13684,9 @@
       <c r="N273" s="10"/>
     </row>
     <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A274" s="107"/>
-      <c r="B274" s="98" t="s">
-        <v>55</v>
+      <c r="A274" s="123"/>
+      <c r="B274" s="96" t="s">
+        <v>54</v>
       </c>
       <c r="C274" s="11">
         <v>8</v>
@@ -13693,9 +13725,9 @@
       <c r="N274" s="10"/>
     </row>
     <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A275" s="107"/>
-      <c r="B275" s="98" t="s">
-        <v>56</v>
+      <c r="A275" s="123"/>
+      <c r="B275" s="96" t="s">
+        <v>55</v>
       </c>
       <c r="C275" s="11">
         <v>8</v>
@@ -13734,9 +13766,9 @@
       <c r="N275" s="10"/>
     </row>
     <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="107"/>
-      <c r="B276" s="98" t="s">
-        <v>69</v>
+      <c r="A276" s="123"/>
+      <c r="B276" s="96" t="s">
+        <v>68</v>
       </c>
       <c r="C276" s="11">
         <v>8</v>
@@ -13775,7 +13807,7 @@
       <c r="N276" s="10"/>
     </row>
     <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="107"/>
+      <c r="A277" s="123"/>
       <c r="B277" s="85" t="s">
         <v>17</v>
       </c>
@@ -13816,7 +13848,7 @@
       <c r="N277" s="10"/>
     </row>
     <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="107"/>
+      <c r="A278" s="123"/>
       <c r="B278" s="85" t="s">
         <v>26</v>
       </c>
@@ -13857,7 +13889,7 @@
       <c r="N278" s="10"/>
     </row>
     <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="107"/>
+      <c r="A279" s="123"/>
       <c r="B279" s="85" t="s">
         <v>27</v>
       </c>
@@ -13898,7 +13930,7 @@
       <c r="N279" s="10"/>
     </row>
     <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="107"/>
+      <c r="A280" s="123"/>
       <c r="B280" s="85" t="s">
         <v>18</v>
       </c>
@@ -13939,7 +13971,7 @@
       <c r="N280" s="10"/>
     </row>
     <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="107"/>
+      <c r="A281" s="123"/>
       <c r="B281" s="85" t="s">
         <v>39</v>
       </c>
@@ -13979,10 +14011,10 @@
       </c>
       <c r="N281" s="10"/>
     </row>
-    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="107"/>
-      <c r="B282" s="101" t="s">
-        <v>70</v>
+    <row r="282" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="123"/>
+      <c r="B282" s="99" t="s">
+        <v>69</v>
       </c>
       <c r="C282" s="11">
         <v>8</v>
@@ -14020,9 +14052,9 @@
       </c>
       <c r="N282" s="10"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A283" s="107"/>
-      <c r="B283" s="87" t="s">
+    <row r="283" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A283" s="123"/>
+      <c r="B283" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C283" s="15">
@@ -14061,9 +14093,9 @@
       </c>
       <c r="N283" s="10"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A284" s="107"/>
-      <c r="B284" s="87" t="s">
+    <row r="284" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A284" s="123"/>
+      <c r="B284" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C284" s="15">
@@ -14103,9 +14135,9 @@
       <c r="N284" s="10"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A285" s="107"/>
-      <c r="B285" s="99" t="s">
-        <v>85</v>
+      <c r="A285" s="123"/>
+      <c r="B285" s="97" t="s">
+        <v>82</v>
       </c>
       <c r="C285" s="11">
         <v>9</v>
@@ -14142,10 +14174,10 @@
       </c>
       <c r="N285" s="10"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A286" s="107"/>
-      <c r="B286" s="102" t="s">
-        <v>88</v>
+    <row r="286" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A286" s="123"/>
+      <c r="B286" s="100" t="s">
+        <v>85</v>
       </c>
       <c r="C286" s="11">
         <v>9</v>
@@ -14182,9 +14214,9 @@
       <c r="N286" s="10"/>
     </row>
     <row r="287" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="108"/>
-      <c r="B287" s="103" t="s">
-        <v>89</v>
+      <c r="A287" s="124"/>
+      <c r="B287" s="101" t="s">
+        <v>86</v>
       </c>
       <c r="C287" s="31">
         <v>9</v>
@@ -14213,14 +14245,14 @@
       <c r="N287" s="10"/>
     </row>
     <row r="288" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="106" t="s">
-        <v>87</v>
-      </c>
-      <c r="B288" s="96" t="s">
-        <v>48</v>
+      <c r="A288" s="122" t="s">
+        <v>84</v>
+      </c>
+      <c r="B288" s="94" t="s">
+        <v>47</v>
       </c>
       <c r="C288" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D288" s="50" t="s">
         <v>19</v>
@@ -14256,12 +14288,12 @@
       <c r="N288" s="10"/>
     </row>
     <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="107"/>
-      <c r="B289" s="97" t="s">
-        <v>50</v>
+      <c r="A289" s="123"/>
+      <c r="B289" s="95" t="s">
+        <v>49</v>
       </c>
       <c r="C289" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>19</v>
@@ -14297,12 +14329,12 @@
       <c r="N289" s="10"/>
     </row>
     <row r="290" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="107"/>
-      <c r="B290" s="97" t="s">
-        <v>64</v>
+      <c r="A290" s="123"/>
+      <c r="B290" s="95" t="s">
+        <v>63</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>19</v>
@@ -14338,8 +14370,8 @@
       <c r="N290" s="10"/>
     </row>
     <row r="291" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="107"/>
-      <c r="B291" s="97" t="s">
+      <c r="A291" s="123"/>
+      <c r="B291" s="95" t="s">
         <v>43</v>
       </c>
       <c r="C291" s="11">
@@ -14379,9 +14411,9 @@
       <c r="N291" s="10"/>
     </row>
     <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="107"/>
-      <c r="B292" s="97" t="s">
-        <v>45</v>
+      <c r="A292" s="123"/>
+      <c r="B292" s="95" t="s">
+        <v>44</v>
       </c>
       <c r="C292" s="11">
         <v>5</v>
@@ -14420,9 +14452,9 @@
       <c r="N292" s="10"/>
     </row>
     <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="107"/>
-      <c r="B293" s="98" t="s">
-        <v>52</v>
+      <c r="A293" s="123"/>
+      <c r="B293" s="96" t="s">
+        <v>51</v>
       </c>
       <c r="C293" s="11">
         <v>6</v>
@@ -14461,9 +14493,9 @@
       <c r="N293" s="10"/>
     </row>
     <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="107"/>
-      <c r="B294" s="98" t="s">
-        <v>53</v>
+      <c r="A294" s="123"/>
+      <c r="B294" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C294" s="11">
         <v>8</v>
@@ -14502,9 +14534,9 @@
       <c r="N294" s="10"/>
     </row>
     <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="107"/>
-      <c r="B295" s="98" t="s">
-        <v>54</v>
+      <c r="A295" s="123"/>
+      <c r="B295" s="96" t="s">
+        <v>53</v>
       </c>
       <c r="C295" s="11">
         <v>8</v>
@@ -14543,9 +14575,9 @@
       <c r="N295" s="10"/>
     </row>
     <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="107"/>
-      <c r="B296" s="98" t="s">
-        <v>55</v>
+      <c r="A296" s="123"/>
+      <c r="B296" s="96" t="s">
+        <v>54</v>
       </c>
       <c r="C296" s="11">
         <v>8</v>
@@ -14584,9 +14616,9 @@
       <c r="N296" s="10"/>
     </row>
     <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A297" s="107"/>
-      <c r="B297" s="98" t="s">
-        <v>56</v>
+      <c r="A297" s="123"/>
+      <c r="B297" s="96" t="s">
+        <v>55</v>
       </c>
       <c r="C297" s="11">
         <v>8</v>
@@ -14625,9 +14657,9 @@
       <c r="N297" s="10"/>
     </row>
     <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="107"/>
-      <c r="B298" s="98" t="s">
-        <v>69</v>
+      <c r="A298" s="123"/>
+      <c r="B298" s="96" t="s">
+        <v>68</v>
       </c>
       <c r="C298" s="11">
         <v>8</v>
@@ -14666,7 +14698,7 @@
       <c r="N298" s="10"/>
     </row>
     <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A299" s="107"/>
+      <c r="A299" s="123"/>
       <c r="B299" s="85" t="s">
         <v>16</v>
       </c>
@@ -14707,7 +14739,7 @@
       <c r="N299" s="10"/>
     </row>
     <row r="300" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="107"/>
+      <c r="A300" s="123"/>
       <c r="B300" s="85" t="s">
         <v>17</v>
       </c>
@@ -14748,7 +14780,7 @@
       <c r="N300" s="10"/>
     </row>
     <row r="301" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="107"/>
+      <c r="A301" s="123"/>
       <c r="B301" s="85" t="s">
         <v>26</v>
       </c>
@@ -14789,7 +14821,7 @@
       <c r="N301" s="10"/>
     </row>
     <row r="302" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="107"/>
+      <c r="A302" s="123"/>
       <c r="B302" s="85" t="s">
         <v>27</v>
       </c>
@@ -14830,7 +14862,7 @@
       <c r="N302" s="10"/>
     </row>
     <row r="303" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="107"/>
+      <c r="A303" s="123"/>
       <c r="B303" s="85" t="s">
         <v>39</v>
       </c>
@@ -14870,9 +14902,9 @@
       </c>
       <c r="N303" s="10"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A304" s="107"/>
-      <c r="B304" s="87" t="s">
+    <row r="304" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A304" s="123"/>
+      <c r="B304" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C304" s="11">
@@ -14911,9 +14943,9 @@
       </c>
       <c r="N304" s="10"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A305" s="107"/>
-      <c r="B305" s="87" t="s">
+    <row r="305" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A305" s="123"/>
+      <c r="B305" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C305" s="11">
@@ -14952,9 +14984,9 @@
       </c>
       <c r="N305" s="10"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A306" s="107"/>
-      <c r="B306" s="87" t="s">
+    <row r="306" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A306" s="123"/>
+      <c r="B306" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C306" s="15">
@@ -14993,9 +15025,9 @@
       </c>
       <c r="N306" s="10"/>
     </row>
-    <row r="307" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="108"/>
-      <c r="B307" s="91" t="s">
+    <row r="307" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A307" s="124"/>
+      <c r="B307" s="89" t="s">
         <v>24</v>
       </c>
       <c r="C307" s="56">
@@ -15035,14 +15067,14 @@
       <c r="N307" s="10"/>
     </row>
     <row r="308" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A308" s="106" t="s">
-        <v>72</v>
-      </c>
-      <c r="B308" s="96" t="s">
-        <v>48</v>
+      <c r="A308" s="122" t="s">
+        <v>71</v>
+      </c>
+      <c r="B308" s="141" t="s">
+        <v>94</v>
       </c>
       <c r="C308" s="34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D308" s="50" t="s">
         <v>19</v>
@@ -15078,12 +15110,12 @@
       <c r="N308" s="10"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A309" s="107"/>
-      <c r="B309" s="97" t="s">
-        <v>50</v>
+      <c r="A309" s="123"/>
+      <c r="B309" s="95" t="s">
+        <v>49</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D309" s="3" t="s">
         <v>19</v>
@@ -15119,12 +15151,12 @@
       <c r="N309" s="10"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A310" s="107"/>
-      <c r="B310" s="97" t="s">
-        <v>64</v>
+      <c r="A310" s="123"/>
+      <c r="B310" s="142" t="s">
+        <v>98</v>
       </c>
       <c r="C310" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D310" s="3" t="s">
         <v>19</v>
@@ -15160,9 +15192,9 @@
       <c r="N310" s="10"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A311" s="107"/>
-      <c r="B311" s="97" t="s">
-        <v>43</v>
+      <c r="A311" s="123"/>
+      <c r="B311" s="142" t="s">
+        <v>91</v>
       </c>
       <c r="C311" s="11">
         <v>5</v>
@@ -15201,9 +15233,9 @@
       <c r="N311" s="10"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A312" s="107"/>
-      <c r="B312" s="97" t="s">
-        <v>45</v>
+      <c r="A312" s="123"/>
+      <c r="B312" s="142" t="s">
+        <v>93</v>
       </c>
       <c r="C312" s="11">
         <v>5</v>
@@ -15242,9 +15274,9 @@
       <c r="N312" s="10"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A313" s="107"/>
-      <c r="B313" s="98" t="s">
-        <v>52</v>
+      <c r="A313" s="123"/>
+      <c r="B313" s="96" t="s">
+        <v>51</v>
       </c>
       <c r="C313" s="11">
         <v>6</v>
@@ -15283,9 +15315,9 @@
       <c r="N313" s="10"/>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A314" s="107"/>
-      <c r="B314" s="98" t="s">
-        <v>53</v>
+      <c r="A314" s="123"/>
+      <c r="B314" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C314" s="11">
         <v>6</v>
@@ -15324,9 +15356,9 @@
       <c r="N314" s="10"/>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A315" s="107"/>
-      <c r="B315" s="98" t="s">
-        <v>54</v>
+      <c r="A315" s="123"/>
+      <c r="B315" s="143" t="s">
+        <v>95</v>
       </c>
       <c r="C315" s="11">
         <v>6</v>
@@ -15365,9 +15397,9 @@
       <c r="N315" s="10"/>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A316" s="107"/>
-      <c r="B316" s="98" t="s">
-        <v>55</v>
+      <c r="A316" s="123"/>
+      <c r="B316" s="143" t="s">
+        <v>96</v>
       </c>
       <c r="C316" s="11">
         <v>6</v>
@@ -15406,9 +15438,9 @@
       <c r="N316" s="10"/>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A317" s="107"/>
-      <c r="B317" s="98" t="s">
-        <v>56</v>
+      <c r="A317" s="123"/>
+      <c r="B317" s="143" t="s">
+        <v>97</v>
       </c>
       <c r="C317" s="11">
         <v>6</v>
@@ -15447,7 +15479,7 @@
       <c r="N317" s="10"/>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A318" s="107"/>
+      <c r="A318" s="123"/>
       <c r="B318" s="85" t="s">
         <v>16</v>
       </c>
@@ -15488,7 +15520,7 @@
       <c r="N318" s="10"/>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A319" s="107"/>
+      <c r="A319" s="123"/>
       <c r="B319" s="85" t="s">
         <v>17</v>
       </c>
@@ -15529,7 +15561,7 @@
       <c r="N319" s="10"/>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A320" s="107"/>
+      <c r="A320" s="123"/>
       <c r="B320" s="85" t="s">
         <v>26</v>
       </c>
@@ -15570,9 +15602,9 @@
       <c r="N320" s="10"/>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A321" s="107"/>
-      <c r="B321" s="85" t="s">
-        <v>27</v>
+      <c r="A321" s="123"/>
+      <c r="B321" s="139" t="s">
+        <v>89</v>
       </c>
       <c r="C321" s="11">
         <v>7</v>
@@ -15611,9 +15643,9 @@
       <c r="N321" s="10"/>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A322" s="107"/>
-      <c r="B322" s="95" t="s">
-        <v>39</v>
+      <c r="A322" s="123"/>
+      <c r="B322" s="93" t="s">
+        <v>90</v>
       </c>
       <c r="C322" s="8">
         <v>7</v>
@@ -15651,9 +15683,9 @@
       </c>
       <c r="N322" s="10"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A323" s="107"/>
-      <c r="B323" s="87" t="s">
+    <row r="323" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A323" s="123"/>
+      <c r="B323" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C323" s="11">
@@ -15692,9 +15724,9 @@
       </c>
       <c r="N323" s="10"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A324" s="107"/>
-      <c r="B324" s="87" t="s">
+    <row r="324" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A324" s="123"/>
+      <c r="B324" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C324" s="11">
@@ -15733,10 +15765,10 @@
       </c>
       <c r="N324" s="10"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A325" s="107"/>
-      <c r="B325" s="87" t="s">
-        <v>73</v>
+    <row r="325" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A325" s="123"/>
+      <c r="B325" s="86" t="s">
+        <v>72</v>
       </c>
       <c r="C325" s="11">
         <v>9</v>
@@ -15774,9 +15806,9 @@
       </c>
       <c r="N325" s="10"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A326" s="107"/>
-      <c r="B326" s="87" t="s">
+    <row r="326" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A326" s="123"/>
+      <c r="B326" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C326" s="15">
@@ -15815,9 +15847,9 @@
       </c>
       <c r="N326" s="10"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A327" s="107"/>
-      <c r="B327" s="87" t="s">
+    <row r="327" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A327" s="123"/>
+      <c r="B327" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C327" s="15">
@@ -15856,10 +15888,10 @@
       </c>
       <c r="N327" s="10"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A328" s="107"/>
-      <c r="B328" s="87" t="s">
-        <v>74</v>
+    <row r="328" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A328" s="123"/>
+      <c r="B328" s="86" t="s">
+        <v>73</v>
       </c>
       <c r="C328" s="15">
         <v>9</v>
@@ -15898,9 +15930,9 @@
       <c r="N328" s="10"/>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A329" s="107"/>
-      <c r="B329" s="99" t="s">
-        <v>85</v>
+      <c r="A329" s="123"/>
+      <c r="B329" s="97" t="s">
+        <v>82</v>
       </c>
       <c r="C329" s="11">
         <v>9</v>
@@ -15939,9 +15971,9 @@
       <c r="N329" s="10"/>
     </row>
     <row r="330" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A330" s="108"/>
-      <c r="B330" s="100" t="s">
-        <v>88</v>
+      <c r="A330" s="124"/>
+      <c r="B330" s="98" t="s">
+        <v>85</v>
       </c>
       <c r="C330" s="31">
         <v>9</v>
@@ -15980,14 +16012,14 @@
       <c r="N330" s="10"/>
     </row>
     <row r="331" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A331" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="B331" s="96" t="s">
-        <v>48</v>
+      <c r="A331" s="122" t="s">
+        <v>74</v>
+      </c>
+      <c r="B331" s="141" t="s">
+        <v>94</v>
       </c>
       <c r="C331" s="34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D331" s="35" t="s">
         <v>34</v>
@@ -16023,12 +16055,12 @@
       <c r="N331" s="10"/>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A332" s="107"/>
-      <c r="B332" s="97" t="s">
-        <v>50</v>
+      <c r="A332" s="123"/>
+      <c r="B332" s="95" t="s">
+        <v>49</v>
       </c>
       <c r="C332" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D332" s="5" t="s">
         <v>34</v>
@@ -16064,9 +16096,9 @@
       <c r="N332" s="10"/>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A333" s="107"/>
-      <c r="B333" s="97" t="s">
-        <v>43</v>
+      <c r="A333" s="123"/>
+      <c r="B333" s="142" t="s">
+        <v>91</v>
       </c>
       <c r="C333" s="11">
         <v>6</v>
@@ -16105,9 +16137,9 @@
       <c r="N333" s="10"/>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A334" s="107"/>
-      <c r="B334" s="97" t="s">
-        <v>45</v>
+      <c r="A334" s="123"/>
+      <c r="B334" s="142" t="s">
+        <v>93</v>
       </c>
       <c r="C334" s="11">
         <v>6</v>
@@ -16146,9 +16178,9 @@
       <c r="N334" s="10"/>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A335" s="107"/>
-      <c r="B335" s="98" t="s">
-        <v>52</v>
+      <c r="A335" s="123"/>
+      <c r="B335" s="96" t="s">
+        <v>51</v>
       </c>
       <c r="C335" s="11">
         <v>8</v>
@@ -16187,9 +16219,9 @@
       <c r="N335" s="10"/>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A336" s="107"/>
-      <c r="B336" s="98" t="s">
-        <v>53</v>
+      <c r="A336" s="123"/>
+      <c r="B336" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C336" s="11">
         <v>8</v>
@@ -16228,9 +16260,9 @@
       <c r="N336" s="10"/>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A337" s="107"/>
-      <c r="B337" s="98" t="s">
-        <v>54</v>
+      <c r="A337" s="123"/>
+      <c r="B337" s="143" t="s">
+        <v>95</v>
       </c>
       <c r="C337" s="11">
         <v>8</v>
@@ -16269,9 +16301,9 @@
       <c r="N337" s="10"/>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A338" s="107"/>
-      <c r="B338" s="98" t="s">
-        <v>55</v>
+      <c r="A338" s="123"/>
+      <c r="B338" s="143" t="s">
+        <v>96</v>
       </c>
       <c r="C338" s="11">
         <v>8</v>
@@ -16310,9 +16342,9 @@
       <c r="N338" s="10"/>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A339" s="107"/>
-      <c r="B339" s="98" t="s">
-        <v>56</v>
+      <c r="A339" s="123"/>
+      <c r="B339" s="143" t="s">
+        <v>97</v>
       </c>
       <c r="C339" s="11">
         <v>8</v>
@@ -16351,7 +16383,7 @@
       <c r="N339" s="10"/>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A340" s="107"/>
+      <c r="A340" s="123"/>
       <c r="B340" s="85" t="s">
         <v>17</v>
       </c>
@@ -16392,7 +16424,7 @@
       <c r="N340" s="10"/>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A341" s="107"/>
+      <c r="A341" s="123"/>
       <c r="B341" s="85" t="s">
         <v>26</v>
       </c>
@@ -16433,9 +16465,9 @@
       <c r="N341" s="10"/>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A342" s="107"/>
-      <c r="B342" s="85" t="s">
-        <v>27</v>
+      <c r="A342" s="123"/>
+      <c r="B342" s="139" t="s">
+        <v>89</v>
       </c>
       <c r="C342" s="11">
         <v>9</v>
@@ -16474,9 +16506,9 @@
       <c r="N342" s="10"/>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A343" s="107"/>
-      <c r="B343" s="85" t="s">
-        <v>18</v>
+      <c r="A343" s="123"/>
+      <c r="B343" s="139" t="s">
+        <v>88</v>
       </c>
       <c r="C343" s="11">
         <v>9</v>
@@ -16515,9 +16547,9 @@
       <c r="N343" s="10"/>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A344" s="107"/>
-      <c r="B344" s="85" t="s">
-        <v>39</v>
+      <c r="A344" s="123"/>
+      <c r="B344" s="139" t="s">
+        <v>90</v>
       </c>
       <c r="C344" s="11">
         <v>9</v>
@@ -16555,10 +16587,10 @@
       </c>
       <c r="N344" s="10"/>
     </row>
-    <row r="345" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A345" s="107"/>
-      <c r="B345" s="101" t="s">
-        <v>70</v>
+    <row r="345" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A345" s="123"/>
+      <c r="B345" s="99" t="s">
+        <v>69</v>
       </c>
       <c r="C345" s="11">
         <v>9</v>
@@ -16596,9 +16628,9 @@
       </c>
       <c r="N345" s="10"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A346" s="107"/>
-      <c r="B346" s="87" t="s">
+    <row r="346" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A346" s="123"/>
+      <c r="B346" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C346" s="11">
@@ -16637,9 +16669,9 @@
       </c>
       <c r="N346" s="10"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A347" s="107"/>
-      <c r="B347" s="87" t="s">
+    <row r="347" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A347" s="123"/>
+      <c r="B347" s="86" t="s">
         <v>21</v>
       </c>
       <c r="C347" s="11">
@@ -16678,10 +16710,10 @@
       </c>
       <c r="N347" s="10"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A348" s="107"/>
-      <c r="B348" s="87" t="s">
-        <v>73</v>
+    <row r="348" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A348" s="123"/>
+      <c r="B348" s="86" t="s">
+        <v>72</v>
       </c>
       <c r="C348" s="11">
         <v>10</v>
@@ -16719,9 +16751,9 @@
       </c>
       <c r="N348" s="10"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A349" s="107"/>
-      <c r="B349" s="87" t="s">
+    <row r="349" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A349" s="123"/>
+      <c r="B349" s="86" t="s">
         <v>23</v>
       </c>
       <c r="C349" s="15">
@@ -16760,9 +16792,9 @@
       </c>
       <c r="N349" s="10"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A350" s="107"/>
-      <c r="B350" s="87" t="s">
+    <row r="350" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A350" s="123"/>
+      <c r="B350" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C350" s="15">
@@ -16801,10 +16833,10 @@
       </c>
       <c r="N350" s="10"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A351" s="107"/>
-      <c r="B351" s="87" t="s">
-        <v>74</v>
+    <row r="351" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A351" s="123"/>
+      <c r="B351" s="86" t="s">
+        <v>73</v>
       </c>
       <c r="C351" s="15">
         <v>10</v>
@@ -16843,9 +16875,9 @@
       <c r="N351" s="10"/>
     </row>
     <row r="352" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A352" s="107"/>
-      <c r="B352" s="99" t="s">
-        <v>85</v>
+      <c r="A352" s="123"/>
+      <c r="B352" s="97" t="s">
+        <v>82</v>
       </c>
       <c r="C352" s="11">
         <v>10</v>
@@ -16883,10 +16915,10 @@
       </c>
       <c r="N352" s="10"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A353" s="107"/>
-      <c r="B353" s="102" t="s">
-        <v>88</v>
+    <row r="353" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A353" s="123"/>
+      <c r="B353" s="100" t="s">
+        <v>85</v>
       </c>
       <c r="C353" s="11">
         <v>10</v>
@@ -16922,10 +16954,10 @@
       </c>
       <c r="N353" s="10"/>
     </row>
-    <row r="354" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="107"/>
-      <c r="B354" s="116" t="s">
-        <v>89</v>
+    <row r="354" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="123"/>
+      <c r="B354" s="103" t="s">
+        <v>86</v>
       </c>
       <c r="C354" s="11">
         <v>10</v>
@@ -16953,53 +16985,53 @@
       </c>
       <c r="N354" s="10"/>
     </row>
-    <row r="355" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A355" s="117" t="s">
-        <v>76</v>
-      </c>
-      <c r="B355" s="137" t="s">
-        <v>66</v>
-      </c>
-      <c r="C355" s="118">
+    <row r="355" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A355" s="133" t="s">
+        <v>75</v>
+      </c>
+      <c r="B355" s="146" t="s">
+        <v>99</v>
+      </c>
+      <c r="C355" s="104">
         <v>8</v>
       </c>
-      <c r="D355" s="119" t="s">
-        <v>15</v>
-      </c>
-      <c r="E355" s="120">
+      <c r="D355" s="105" t="s">
+        <v>15</v>
+      </c>
+      <c r="E355" s="106">
         <v>9.9659999999999993</v>
       </c>
-      <c r="F355" s="120">
+      <c r="F355" s="106">
         <v>9.9</v>
       </c>
-      <c r="G355" s="120">
+      <c r="G355" s="106">
         <v>10.9</v>
       </c>
-      <c r="H355" s="120">
+      <c r="H355" s="106">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I355" s="120">
+      <c r="I355" s="106">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J355" s="120">
+      <c r="J355" s="106">
         <v>10.95</v>
       </c>
-      <c r="K355" s="121" cm="1">
+      <c r="K355" s="107" cm="1">
         <f t="array" ref="K355">SUM(E355:J355)</f>
         <v>56.116</v>
       </c>
-      <c r="L355" s="118">
+      <c r="L355" s="104">
         <v>4</v>
       </c>
-      <c r="M355" s="122">
+      <c r="M355" s="108">
         <v>6</v>
       </c>
       <c r="N355" s="10"/>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A356" s="123"/>
-      <c r="B356" s="138" t="s">
-        <v>64</v>
+      <c r="A356" s="134"/>
+      <c r="B356" s="147" t="s">
+        <v>98</v>
       </c>
       <c r="C356" s="11">
         <v>9</v>
@@ -17032,15 +17064,15 @@
       <c r="L356" s="11">
         <v>25</v>
       </c>
-      <c r="M356" s="124">
+      <c r="M356" s="109">
         <v>35</v>
       </c>
       <c r="N356" s="10"/>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A357" s="123"/>
-      <c r="B357" s="138" t="s">
-        <v>43</v>
+      <c r="A357" s="134"/>
+      <c r="B357" s="147" t="s">
+        <v>91</v>
       </c>
       <c r="C357" s="11">
         <v>9</v>
@@ -17073,15 +17105,15 @@
       <c r="L357" s="11">
         <v>4</v>
       </c>
-      <c r="M357" s="124">
+      <c r="M357" s="109">
         <v>7</v>
       </c>
       <c r="N357" s="10"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A358" s="123"/>
-      <c r="B358" s="138" t="s">
-        <v>45</v>
+      <c r="A358" s="134"/>
+      <c r="B358" s="147" t="s">
+        <v>93</v>
       </c>
       <c r="C358" s="11">
         <v>9</v>
@@ -17114,14 +17146,14 @@
       <c r="L358" s="11">
         <v>10</v>
       </c>
-      <c r="M358" s="124">
+      <c r="M358" s="109">
         <v>27</v>
       </c>
       <c r="N358" s="10"/>
     </row>
     <row r="359" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A359" s="123"/>
-      <c r="B359" s="140" t="s">
+      <c r="A359" s="134"/>
+      <c r="B359" s="115" t="s">
         <v>16</v>
       </c>
       <c r="C359" s="11">
@@ -17151,14 +17183,14 @@
       <c r="L359" s="11">
         <v>37</v>
       </c>
-      <c r="M359" s="124">
+      <c r="M359" s="109">
         <v>42</v>
       </c>
       <c r="N359" s="10"/>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A360" s="123"/>
-      <c r="B360" s="140" t="s">
+      <c r="A360" s="134"/>
+      <c r="B360" s="115" t="s">
         <v>17</v>
       </c>
       <c r="C360" s="11">
@@ -17192,14 +17224,14 @@
       <c r="L360" s="11">
         <v>2</v>
       </c>
-      <c r="M360" s="124">
+      <c r="M360" s="109">
         <v>7</v>
       </c>
       <c r="N360" s="10"/>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A361" s="123"/>
-      <c r="B361" s="140" t="s">
+      <c r="A361" s="134"/>
+      <c r="B361" s="115" t="s">
         <v>26</v>
       </c>
       <c r="C361" s="11">
@@ -17233,15 +17265,15 @@
       <c r="L361" s="11">
         <v>2</v>
       </c>
-      <c r="M361" s="124">
+      <c r="M361" s="109">
         <v>2</v>
       </c>
       <c r="N361" s="10"/>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A362" s="123"/>
-      <c r="B362" s="140" t="s">
-        <v>27</v>
+      <c r="A362" s="134"/>
+      <c r="B362" s="145" t="s">
+        <v>89</v>
       </c>
       <c r="C362" s="11">
         <v>10</v>
@@ -17274,15 +17306,15 @@
       <c r="L362" s="11">
         <v>3</v>
       </c>
-      <c r="M362" s="124">
+      <c r="M362" s="109">
         <v>5</v>
       </c>
       <c r="N362" s="10"/>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A363" s="123"/>
-      <c r="B363" s="140" t="s">
-        <v>18</v>
+      <c r="A363" s="134"/>
+      <c r="B363" s="145" t="s">
+        <v>88</v>
       </c>
       <c r="C363" s="11">
         <v>10</v>
@@ -17315,15 +17347,15 @@
       <c r="L363" s="11">
         <v>4</v>
       </c>
-      <c r="M363" s="124">
+      <c r="M363" s="109">
         <v>9</v>
       </c>
       <c r="N363" s="10"/>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A364" s="123"/>
-      <c r="B364" s="140" t="s">
-        <v>39</v>
+      <c r="A364" s="134"/>
+      <c r="B364" s="145" t="s">
+        <v>90</v>
       </c>
       <c r="C364" s="11">
         <v>10</v>
@@ -17356,14 +17388,14 @@
       <c r="L364" s="11">
         <v>23</v>
       </c>
-      <c r="M364" s="124">
+      <c r="M364" s="109">
         <v>35</v>
       </c>
       <c r="N364" s="10"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A365" s="123"/>
-      <c r="B365" s="142" t="s">
+    <row r="365" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A365" s="134"/>
+      <c r="B365" s="117" t="s">
         <v>20</v>
       </c>
       <c r="C365" s="11">
@@ -17397,14 +17429,14 @@
       <c r="L365" s="11">
         <v>1</v>
       </c>
-      <c r="M365" s="124">
+      <c r="M365" s="109">
         <v>2</v>
       </c>
       <c r="N365" s="10"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A366" s="123"/>
-      <c r="B366" s="142" t="s">
+    <row r="366" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A366" s="134"/>
+      <c r="B366" s="117" t="s">
         <v>21</v>
       </c>
       <c r="C366" s="11">
@@ -17438,15 +17470,15 @@
       <c r="L366" s="11">
         <v>4</v>
       </c>
-      <c r="M366" s="124">
+      <c r="M366" s="109">
         <v>6</v>
       </c>
       <c r="N366" s="10"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A367" s="123"/>
-      <c r="B367" s="142" t="s">
-        <v>73</v>
+    <row r="367" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A367" s="134"/>
+      <c r="B367" s="117" t="s">
+        <v>72</v>
       </c>
       <c r="C367" s="11">
         <v>10</v>
@@ -17479,14 +17511,14 @@
       <c r="L367" s="11">
         <v>15</v>
       </c>
-      <c r="M367" s="124">
+      <c r="M367" s="109">
         <v>30</v>
       </c>
       <c r="N367" s="10"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A368" s="123"/>
-      <c r="B368" s="142" t="s">
+    <row r="368" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A368" s="134"/>
+      <c r="B368" s="117" t="s">
         <v>24</v>
       </c>
       <c r="C368" s="11">
@@ -17520,15 +17552,15 @@
       <c r="L368" s="11">
         <v>1</v>
       </c>
-      <c r="M368" s="124">
+      <c r="M368" s="109">
         <v>3</v>
       </c>
       <c r="N368" s="10"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A369" s="123"/>
-      <c r="B369" s="142" t="s">
-        <v>74</v>
+    <row r="369" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A369" s="134"/>
+      <c r="B369" s="117" t="s">
+        <v>73</v>
       </c>
       <c r="C369" s="11">
         <v>10</v>
@@ -17561,15 +17593,15 @@
       <c r="L369" s="11">
         <v>12</v>
       </c>
-      <c r="M369" s="124">
+      <c r="M369" s="109">
         <v>28</v>
       </c>
       <c r="N369" s="10"/>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A370" s="123"/>
-      <c r="B370" s="143" t="s">
-        <v>85</v>
+      <c r="A370" s="134"/>
+      <c r="B370" s="118" t="s">
+        <v>82</v>
       </c>
       <c r="C370" s="11">
         <v>10</v>
@@ -17601,15 +17633,15 @@
       <c r="L370" s="11">
         <v>9</v>
       </c>
-      <c r="M370" s="124">
+      <c r="M370" s="109">
         <v>34</v>
       </c>
       <c r="N370" s="10"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A371" s="123"/>
-      <c r="B371" s="144" t="s">
-        <v>88</v>
+    <row r="371" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A371" s="134"/>
+      <c r="B371" s="119" t="s">
+        <v>85</v>
       </c>
       <c r="C371" s="11">
         <v>10</v>
@@ -17642,15 +17674,15 @@
       <c r="L371" s="11">
         <v>7</v>
       </c>
-      <c r="M371" s="124">
+      <c r="M371" s="109">
         <v>22</v>
       </c>
       <c r="N371" s="10"/>
     </row>
     <row r="372" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A372" s="123"/>
-      <c r="B372" s="146" t="s">
-        <v>89</v>
+      <c r="A372" s="134"/>
+      <c r="B372" s="121" t="s">
+        <v>86</v>
       </c>
       <c r="C372" s="11">
         <v>10</v>
@@ -17675,17 +17707,17 @@
         <v>33.832000000000001</v>
       </c>
       <c r="L372" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="M372" s="124">
+        <v>87</v>
+      </c>
+      <c r="M372" s="109">
         <v>8</v>
       </c>
       <c r="N372" s="10"/>
     </row>
     <row r="373" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A373" s="123"/>
-      <c r="B373" s="146" t="s">
-        <v>90</v>
+      <c r="A373" s="134"/>
+      <c r="B373" s="121" t="s">
+        <v>100</v>
       </c>
       <c r="C373" s="11">
         <v>10</v>
@@ -17718,15 +17750,15 @@
       <c r="L373" s="11">
         <v>8</v>
       </c>
-      <c r="M373" s="124">
+      <c r="M373" s="109">
         <v>15</v>
       </c>
       <c r="N373" s="10"/>
     </row>
     <row r="374" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A374" s="125"/>
-      <c r="B374" s="145" t="s">
-        <v>92</v>
+      <c r="A374" s="135"/>
+      <c r="B374" s="120" t="s">
+        <v>101</v>
       </c>
       <c r="C374" s="19">
         <v>10</v>
@@ -17734,32 +17766,32 @@
       <c r="D374" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E374" s="126"/>
-      <c r="F374" s="126">
+      <c r="E374" s="110"/>
+      <c r="F374" s="110">
         <v>10.95</v>
       </c>
-      <c r="G374" s="126"/>
-      <c r="H374" s="126"/>
-      <c r="I374" s="126"/>
-      <c r="J374" s="126"/>
-      <c r="K374" s="127">
+      <c r="G374" s="110"/>
+      <c r="H374" s="110"/>
+      <c r="I374" s="110"/>
+      <c r="J374" s="110"/>
+      <c r="K374" s="111">
         <f>SUM(E374:J374)</f>
         <v>10.95</v>
       </c>
       <c r="L374" s="19">
         <v>1</v>
       </c>
-      <c r="M374" s="128">
+      <c r="M374" s="112">
         <v>8</v>
       </c>
       <c r="N374" s="10"/>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A375" s="107" t="s">
-        <v>77</v>
-      </c>
-      <c r="B375" s="97" t="s">
-        <v>50</v>
+      <c r="A375" s="123" t="s">
+        <v>76</v>
+      </c>
+      <c r="B375" s="95" t="s">
+        <v>49</v>
       </c>
       <c r="C375" s="11">
         <v>9</v>
@@ -17798,9 +17830,9 @@
       <c r="N375" s="10"/>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A376" s="107"/>
-      <c r="B376" s="97" t="s">
-        <v>64</v>
+      <c r="A376" s="123"/>
+      <c r="B376" s="142" t="s">
+        <v>98</v>
       </c>
       <c r="C376" s="11">
         <v>9</v>
@@ -17839,9 +17871,9 @@
       <c r="N376" s="10"/>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A377" s="107"/>
-      <c r="B377" s="97" t="s">
-        <v>45</v>
+      <c r="A377" s="123"/>
+      <c r="B377" s="142" t="s">
+        <v>93</v>
       </c>
       <c r="C377" s="11">
         <v>10</v>
@@ -17880,9 +17912,9 @@
       <c r="N377" s="10"/>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A378" s="107"/>
-      <c r="B378" s="97" t="s">
-        <v>68</v>
+      <c r="A378" s="123"/>
+      <c r="B378" s="142" t="s">
+        <v>102</v>
       </c>
       <c r="C378" s="11">
         <v>10</v>
@@ -17921,9 +17953,9 @@
       <c r="N378" s="10"/>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A379" s="107"/>
-      <c r="B379" s="98" t="s">
-        <v>52</v>
+      <c r="A379" s="123"/>
+      <c r="B379" s="96" t="s">
+        <v>51</v>
       </c>
       <c r="C379" s="11">
         <v>10</v>
@@ -17962,9 +17994,9 @@
       <c r="N379" s="10"/>
     </row>
     <row r="380" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A380" s="107"/>
-      <c r="B380" s="98" t="s">
-        <v>78</v>
+      <c r="A380" s="123"/>
+      <c r="B380" s="96" t="s">
+        <v>77</v>
       </c>
       <c r="C380" s="11">
         <v>10</v>
@@ -18003,9 +18035,9 @@
       <c r="N380" s="10"/>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A381" s="107"/>
-      <c r="B381" s="98" t="s">
-        <v>53</v>
+      <c r="A381" s="123"/>
+      <c r="B381" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C381" s="11">
         <v>10</v>
@@ -18044,9 +18076,9 @@
       <c r="N381" s="10"/>
     </row>
     <row r="382" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A382" s="107"/>
-      <c r="B382" s="98" t="s">
-        <v>54</v>
+      <c r="A382" s="123"/>
+      <c r="B382" s="143" t="s">
+        <v>95</v>
       </c>
       <c r="C382" s="11">
         <v>10</v>
@@ -18085,9 +18117,9 @@
       <c r="N382" s="10"/>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A383" s="107"/>
-      <c r="B383" s="98" t="s">
-        <v>56</v>
+      <c r="A383" s="123"/>
+      <c r="B383" s="143" t="s">
+        <v>97</v>
       </c>
       <c r="C383" s="11">
         <v>10</v>
@@ -18126,7 +18158,7 @@
       <c r="N383" s="10"/>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A384" s="107"/>
+      <c r="A384" s="123"/>
       <c r="B384" s="85" t="s">
         <v>16</v>
       </c>
@@ -18167,7 +18199,7 @@
       <c r="N384" s="10"/>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A385" s="107"/>
+      <c r="A385" s="123"/>
       <c r="B385" s="85" t="s">
         <v>26</v>
       </c>
@@ -18208,9 +18240,9 @@
       <c r="N385" s="10"/>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A386" s="107"/>
-      <c r="B386" s="85" t="s">
-        <v>27</v>
+      <c r="A386" s="123"/>
+      <c r="B386" s="139" t="s">
+        <v>89</v>
       </c>
       <c r="C386" s="11">
         <v>10</v>
@@ -18249,9 +18281,9 @@
       <c r="N386" s="10"/>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A387" s="107"/>
-      <c r="B387" s="85" t="s">
-        <v>18</v>
+      <c r="A387" s="123"/>
+      <c r="B387" s="139" t="s">
+        <v>88</v>
       </c>
       <c r="C387" s="11">
         <v>10</v>
@@ -18290,9 +18322,9 @@
       <c r="N387" s="10"/>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A388" s="107"/>
-      <c r="B388" s="85" t="s">
-        <v>39</v>
+      <c r="A388" s="123"/>
+      <c r="B388" s="139" t="s">
+        <v>90</v>
       </c>
       <c r="C388" s="11">
         <v>10</v>
@@ -18330,10 +18362,10 @@
       </c>
       <c r="N388" s="10"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A389" s="107"/>
-      <c r="B389" s="101" t="s">
-        <v>70</v>
+    <row r="389" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A389" s="123"/>
+      <c r="B389" s="99" t="s">
+        <v>69</v>
       </c>
       <c r="C389" s="11">
         <v>10</v>
@@ -18371,13 +18403,13 @@
       </c>
       <c r="N389" s="10"/>
     </row>
-    <row r="390" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A390" s="109"/>
-      <c r="B390" s="104" t="s">
-        <v>73</v>
+    <row r="390" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A390" s="136"/>
+      <c r="B390" s="102" t="s">
+        <v>72</v>
       </c>
       <c r="C390" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D390" s="20" t="s">
         <v>15</v>
@@ -18413,11 +18445,11 @@
       <c r="N390" s="10"/>
     </row>
     <row r="391" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A391" s="107" t="s">
-        <v>80</v>
-      </c>
-      <c r="B391" s="97" t="s">
-        <v>50</v>
+      <c r="A391" s="123" t="s">
+        <v>79</v>
+      </c>
+      <c r="B391" s="95" t="s">
+        <v>49</v>
       </c>
       <c r="C391" s="11">
         <v>10</v>
@@ -18456,9 +18488,9 @@
       <c r="N391" s="10"/>
     </row>
     <row r="392" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A392" s="107"/>
-      <c r="B392" s="105" t="s">
-        <v>81</v>
+      <c r="A392" s="123"/>
+      <c r="B392" s="148" t="s">
+        <v>103</v>
       </c>
       <c r="C392" s="11">
         <v>10</v>
@@ -18497,9 +18529,9 @@
       <c r="N392" s="10"/>
     </row>
     <row r="393" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A393" s="107"/>
-      <c r="B393" s="97" t="s">
-        <v>45</v>
+      <c r="A393" s="123"/>
+      <c r="B393" s="142" t="s">
+        <v>93</v>
       </c>
       <c r="C393" s="11">
         <v>10</v>
@@ -18538,9 +18570,9 @@
       <c r="N393" s="10"/>
     </row>
     <row r="394" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A394" s="107"/>
-      <c r="B394" s="97" t="s">
-        <v>68</v>
+      <c r="A394" s="123"/>
+      <c r="B394" s="142" t="s">
+        <v>102</v>
       </c>
       <c r="C394" s="11">
         <v>10</v>
@@ -18579,9 +18611,9 @@
       <c r="N394" s="10"/>
     </row>
     <row r="395" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A395" s="107"/>
-      <c r="B395" s="98" t="s">
-        <v>52</v>
+      <c r="A395" s="123"/>
+      <c r="B395" s="96" t="s">
+        <v>51</v>
       </c>
       <c r="C395" s="11">
         <v>10</v>
@@ -18620,9 +18652,9 @@
       <c r="N395" s="10"/>
     </row>
     <row r="396" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A396" s="107"/>
-      <c r="B396" s="98" t="s">
-        <v>78</v>
+      <c r="A396" s="123"/>
+      <c r="B396" s="96" t="s">
+        <v>77</v>
       </c>
       <c r="C396" s="11">
         <v>10</v>
@@ -18661,9 +18693,9 @@
       <c r="N396" s="10"/>
     </row>
     <row r="397" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A397" s="107"/>
-      <c r="B397" s="98" t="s">
-        <v>53</v>
+      <c r="A397" s="123"/>
+      <c r="B397" s="96" t="s">
+        <v>52</v>
       </c>
       <c r="C397" s="11">
         <v>10</v>
@@ -18702,9 +18734,9 @@
       <c r="N397" s="10"/>
     </row>
     <row r="398" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A398" s="107"/>
-      <c r="B398" s="98" t="s">
-        <v>82</v>
+      <c r="A398" s="123"/>
+      <c r="B398" s="96" t="s">
+        <v>80</v>
       </c>
       <c r="C398" s="11">
         <v>10</v>
@@ -18743,9 +18775,9 @@
       <c r="N398" s="10"/>
     </row>
     <row r="399" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A399" s="107"/>
-      <c r="B399" s="98" t="s">
-        <v>83</v>
+      <c r="A399" s="123"/>
+      <c r="B399" s="143" t="s">
+        <v>104</v>
       </c>
       <c r="C399" s="11">
         <v>10</v>
@@ -18784,9 +18816,9 @@
       <c r="N399" s="10"/>
     </row>
     <row r="400" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A400" s="107"/>
-      <c r="B400" s="98" t="s">
-        <v>56</v>
+      <c r="A400" s="123"/>
+      <c r="B400" s="143" t="s">
+        <v>97</v>
       </c>
       <c r="C400" s="11">
         <v>10</v>
@@ -18825,9 +18857,9 @@
       <c r="N400" s="10"/>
     </row>
     <row r="401" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A401" s="107"/>
-      <c r="B401" s="98" t="s">
-        <v>69</v>
+      <c r="A401" s="123"/>
+      <c r="B401" s="143" t="s">
+        <v>105</v>
       </c>
       <c r="C401" s="11">
         <v>10</v>
@@ -18866,12 +18898,12 @@
       <c r="N401" s="10"/>
     </row>
     <row r="402" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A402" s="107"/>
-      <c r="B402" s="85" t="s">
-        <v>39</v>
+      <c r="A402" s="123"/>
+      <c r="B402" s="139" t="s">
+        <v>90</v>
       </c>
       <c r="C402" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D402" s="2" t="s">
         <v>15</v>
@@ -18907,12 +18939,12 @@
       <c r="N402" s="10"/>
     </row>
     <row r="403" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A403" s="107"/>
+      <c r="A403" s="123"/>
       <c r="B403" s="85" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C403" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D403" s="2" t="s">
         <v>15</v>
@@ -18947,13 +18979,13 @@
       </c>
       <c r="N403" s="10"/>
     </row>
-    <row r="404" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A404" s="108"/>
-      <c r="B404" s="88" t="s">
-        <v>85</v>
+    <row r="404" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A404" s="124"/>
+      <c r="B404" s="87" t="s">
+        <v>82</v>
       </c>
       <c r="C404" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D404" s="32" t="s">
         <v>15</v>
@@ -18992,6 +19024,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A184:A187"/>
+    <mergeCell ref="A375:A390"/>
+    <mergeCell ref="A391:A404"/>
+    <mergeCell ref="A188:A205"/>
+    <mergeCell ref="A308:A330"/>
+    <mergeCell ref="A331:A354"/>
+    <mergeCell ref="A288:A307"/>
+    <mergeCell ref="A266:A287"/>
+    <mergeCell ref="A242:A265"/>
+    <mergeCell ref="A222:A241"/>
+    <mergeCell ref="A206:A221"/>
+    <mergeCell ref="A355:A374"/>
     <mergeCell ref="A166:A183"/>
     <mergeCell ref="A154:A165"/>
     <mergeCell ref="A133:A153"/>
@@ -19008,18 +19052,6 @@
     <mergeCell ref="A74:A79"/>
     <mergeCell ref="A108:A120"/>
     <mergeCell ref="A101:A107"/>
-    <mergeCell ref="A391:A404"/>
-    <mergeCell ref="A188:A205"/>
-    <mergeCell ref="A308:A330"/>
-    <mergeCell ref="A331:A354"/>
-    <mergeCell ref="A288:A307"/>
-    <mergeCell ref="A266:A287"/>
-    <mergeCell ref="A242:A265"/>
-    <mergeCell ref="A222:A241"/>
-    <mergeCell ref="A206:A221"/>
-    <mergeCell ref="A355:A374"/>
-    <mergeCell ref="A184:A187"/>
-    <mergeCell ref="A375:A390"/>
   </mergeCells>
   <conditionalFormatting sqref="L1:L404">
     <cfRule type="cellIs" dxfId="4" priority="60" stopIfTrue="1" operator="between">
